--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C37D8E1-DA5B-4ABC-968B-1F96272F8C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="264">
   <si>
     <t>##var</t>
   </si>
@@ -77,13 +77,925 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>BattlePropertyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前体上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicMaxHp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础体上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHpInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体上限整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHpPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体上限百分比变量</t>
+  </si>
+  <si>
+    <t>AllMaxHpPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体上限外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicHp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllHpPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxGangQi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前刚炁上限</t>
+  </si>
+  <si>
+    <t>BasicMaxGangQi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础刚炁上限</t>
+  </si>
+  <si>
+    <t>MaxGangQiInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁上限整数变量</t>
+  </si>
+  <si>
+    <t>MaxGangQiPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁上限百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllMaxGangQiPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁上限外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前刚炁</t>
+  </si>
+  <si>
+    <t>BasicGangQi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础刚炁</t>
+  </si>
+  <si>
+    <t>GangQiInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁整数变量</t>
+  </si>
+  <si>
+    <t>GangQiPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁百分比变量</t>
+  </si>
+  <si>
+    <t>AllGangQiPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxXuanQi</t>
+  </si>
+  <si>
+    <t>当前玄炁上限</t>
+  </si>
+  <si>
+    <t>BasicMaxXuanQi</t>
+  </si>
+  <si>
+    <t>基础玄炁上限</t>
+  </si>
+  <si>
+    <t>MaxXuanQiInt</t>
+  </si>
+  <si>
+    <t>玄炁上限整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxXuanQiPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁上限百分比变量</t>
+  </si>
+  <si>
+    <t>AllMaxXuanQiPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁上限外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQi</t>
+  </si>
+  <si>
+    <t>当前玄炁</t>
+  </si>
+  <si>
+    <t>BasicXuanQi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础玄炁</t>
+  </si>
+  <si>
+    <t>XuanQiInt</t>
+  </si>
+  <si>
+    <t>玄炁整数变量</t>
+  </si>
+  <si>
+    <t>XuanQiPct</t>
+  </si>
+  <si>
+    <t>玄炁百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllXuanQiPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicPower</t>
+  </si>
+  <si>
+    <t>基础力</t>
+  </si>
+  <si>
+    <t>PowerInt</t>
+  </si>
+  <si>
+    <t>力整数变量</t>
+  </si>
+  <si>
+    <t>PowerPct</t>
+  </si>
+  <si>
+    <t>力百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllPowerPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>力外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tech</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前技</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicTech</t>
+  </si>
+  <si>
+    <t>基础技</t>
+  </si>
+  <si>
+    <t>TechInt</t>
+  </si>
+  <si>
+    <t>技整数变量</t>
+  </si>
+  <si>
+    <t>TechPct</t>
+  </si>
+  <si>
+    <t>技百分比变量</t>
+  </si>
+  <si>
+    <t>AllTechPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前速</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicSpeed</t>
+  </si>
+  <si>
+    <t>基础速</t>
+  </si>
+  <si>
+    <t>SpeedInt</t>
+  </si>
+  <si>
+    <t>速整数变量</t>
+  </si>
+  <si>
+    <t>SpeedPct</t>
+  </si>
+  <si>
+    <t>速百分比变量</t>
+  </si>
+  <si>
+    <t>AllSpeedPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>速外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clever</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前巧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础巧</t>
+  </si>
+  <si>
+    <t>CleverInt</t>
+  </si>
+  <si>
+    <t>巧整数变量</t>
+  </si>
+  <si>
+    <t>CleverPct</t>
+  </si>
+  <si>
+    <t>巧百分比变量</t>
+  </si>
+  <si>
+    <t>AllCleverPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>巧外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defend</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前防</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础防</t>
+  </si>
+  <si>
+    <t>DefendInt</t>
+  </si>
+  <si>
+    <t>防整数变量</t>
+  </si>
+  <si>
+    <t>DefendPct</t>
+  </si>
+  <si>
+    <t>防百分比变量</t>
+  </si>
+  <si>
+    <t>AllDefendPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前破</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础破</t>
+  </si>
+  <si>
+    <t>BreakInt</t>
+  </si>
+  <si>
+    <t>破整数变量</t>
+  </si>
+  <si>
+    <t>BreakPct</t>
+  </si>
+  <si>
+    <t>破百分比变量</t>
+  </si>
+  <si>
+    <t>AllBreakPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>破外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllGangQiRecPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQiRecInt</t>
+  </si>
+  <si>
+    <t>XuanQiRecPct</t>
+  </si>
+  <si>
+    <t>AllXuanQiRecPct</t>
+  </si>
+  <si>
+    <t>KeyUp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyDown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyLeft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyRight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyMax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>键存储最大值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyMaxEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外键存储值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReducePct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害百分比变动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式伤害直接减免</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KillingDamageReduceInt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecNatural</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQiRecNatural</t>
+  </si>
+  <si>
+    <t>当前刚炁自然恢复值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRedInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRedPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllGangQiRedPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前玄炁自然恢复值</t>
+  </si>
+  <si>
+    <t>玄炁恢复整数变量</t>
+  </si>
+  <si>
+    <t>玄炁恢复百分比变量</t>
+  </si>
+  <si>
+    <t>玄炁恢复外围乘区</t>
+  </si>
+  <si>
+    <t>玄炁消耗整数变量</t>
+  </si>
+  <si>
+    <t>玄炁消耗百分比变量</t>
+  </si>
+  <si>
+    <t>玄炁消耗外围乘区</t>
+  </si>
+  <si>
+    <t>XuanQiRedInt</t>
+  </si>
+  <si>
+    <t>XuanQiRedPct</t>
+  </si>
+  <si>
+    <t>AllXuanQiRedPct</t>
+  </si>
+  <si>
+    <t>扳机时刻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoDesitionAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleMomentType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleSource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Treasure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Natural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageRateFloor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowerKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TechniqueImperialStyle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellFormula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>术杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技御式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法咒式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Direct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>间接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InDirect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleClashType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoubleClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单方面行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeUnderAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterClash</t>
+  </si>
+  <si>
+    <t>ReleaseSkillAction</t>
+  </si>
+  <si>
+    <t>AfterUnderAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffOverlayType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗buff叠加类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dispose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发一下马上结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overlap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduceType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff减少逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少一层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叠加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被命中时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleKeyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicBreak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicDefend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicClever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffAdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,8 +1006,22 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -141,17 +1067,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -429,105 +1358,1518 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L139"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="19" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="30.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="1">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="1">
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="1">
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="1">
+        <v>20004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1">
+        <v>20005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="1">
+        <v>20011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="1">
+        <v>20012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="1">
+        <v>20013</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="1">
+        <v>20014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="1">
+        <v>20015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="1">
+        <v>20021</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="1">
+        <v>20022</v>
+      </c>
+    </row>
+    <row r="17" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="1">
+        <v>20023</v>
+      </c>
+    </row>
+    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="1">
+        <v>20024</v>
+      </c>
+    </row>
+    <row r="19" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="1">
+        <v>20025</v>
+      </c>
+    </row>
+    <row r="20" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" s="1">
+        <v>20031</v>
+      </c>
+    </row>
+    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="1">
+        <v>20032</v>
+      </c>
+    </row>
+    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" s="1">
+        <v>20033</v>
+      </c>
+    </row>
+    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23" s="1">
+        <v>20034</v>
+      </c>
+    </row>
+    <row r="24" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="1">
+        <v>20035</v>
+      </c>
+    </row>
+    <row r="25" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J25" s="1">
+        <v>20041</v>
+      </c>
+    </row>
+    <row r="26" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="1">
+        <v>20042</v>
+      </c>
+    </row>
+    <row r="27" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" s="1">
+        <v>20043</v>
+      </c>
+    </row>
+    <row r="28" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28" s="1">
+        <v>20044</v>
+      </c>
+    </row>
+    <row r="29" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J29" s="1">
+        <v>20045</v>
+      </c>
+    </row>
+    <row r="30" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" s="1">
+        <v>20051</v>
+      </c>
+    </row>
+    <row r="31" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="1">
+        <v>20052</v>
+      </c>
+    </row>
+    <row r="32" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J32" s="1">
+        <v>20053</v>
+      </c>
+    </row>
+    <row r="33" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33" s="1">
+        <v>20054</v>
+      </c>
+    </row>
+    <row r="34" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J34" s="1">
+        <v>20055</v>
+      </c>
+    </row>
+    <row r="35" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J35" s="1">
+        <v>20061</v>
+      </c>
+    </row>
+    <row r="36" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" s="1">
+        <v>20062</v>
+      </c>
+    </row>
+    <row r="37" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J37" s="1">
+        <v>20063</v>
+      </c>
+    </row>
+    <row r="38" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J38" s="1">
+        <v>20064</v>
+      </c>
+    </row>
+    <row r="39" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J39" s="1">
+        <v>20065</v>
+      </c>
+    </row>
+    <row r="40" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J40" s="1">
+        <v>20071</v>
+      </c>
+    </row>
+    <row r="41" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J41" s="1">
+        <v>20072</v>
+      </c>
+    </row>
+    <row r="42" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J42" s="1">
+        <v>20073</v>
+      </c>
+    </row>
+    <row r="43" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J43" s="1">
+        <v>20074</v>
+      </c>
+    </row>
+    <row r="44" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J44" s="1">
+        <v>20075</v>
+      </c>
+    </row>
+    <row r="45" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J45" s="1">
+        <v>20081</v>
+      </c>
+    </row>
+    <row r="46" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J46" s="1">
+        <v>20082</v>
+      </c>
+    </row>
+    <row r="47" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H47" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J47" s="1">
+        <v>20083</v>
+      </c>
+    </row>
+    <row r="48" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J48" s="1">
+        <v>20084</v>
+      </c>
+    </row>
+    <row r="49" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J49" s="1">
+        <v>20085</v>
+      </c>
+    </row>
+    <row r="50" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J50" s="1">
+        <v>20091</v>
+      </c>
+    </row>
+    <row r="51" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H51" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J51" s="1">
+        <v>20092</v>
+      </c>
+    </row>
+    <row r="52" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H52" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J52" s="1">
+        <v>20093</v>
+      </c>
+    </row>
+    <row r="53" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J53" s="1">
+        <v>20094</v>
+      </c>
+    </row>
+    <row r="54" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J54" s="1">
+        <v>20095</v>
+      </c>
+    </row>
+    <row r="55" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H55" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J55" s="1">
+        <v>20101</v>
+      </c>
+    </row>
+    <row r="56" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H56" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J56" s="1">
+        <v>20102</v>
+      </c>
+    </row>
+    <row r="57" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H57" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J57" s="1">
+        <v>20103</v>
+      </c>
+    </row>
+    <row r="58" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H58" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J58" s="1">
+        <v>20104</v>
+      </c>
+    </row>
+    <row r="59" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H59" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J59" s="1">
+        <v>20105</v>
+      </c>
+    </row>
+    <row r="60" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H60" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J60" s="1">
+        <v>20111</v>
+      </c>
+    </row>
+    <row r="61" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H61" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J61" s="1">
+        <v>20112</v>
+      </c>
+    </row>
+    <row r="62" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J62" s="1">
+        <v>20113</v>
+      </c>
+    </row>
+    <row r="63" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J63" s="1">
+        <v>20114</v>
+      </c>
+    </row>
+    <row r="64" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J64" s="1">
+        <v>20115</v>
+      </c>
+    </row>
+    <row r="65" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H65" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J65" s="1">
+        <v>20121</v>
+      </c>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H66" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J66" s="1">
+        <v>20122</v>
+      </c>
+    </row>
+    <row r="67" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J67" s="1">
+        <v>20123</v>
+      </c>
+    </row>
+    <row r="68" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H68" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J68" s="1">
+        <v>20124</v>
+      </c>
+    </row>
+    <row r="69" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H69" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J69" s="1">
+        <v>20125</v>
+      </c>
+    </row>
+    <row r="70" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H70" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J70" s="1">
+        <v>20126</v>
+      </c>
+    </row>
+    <row r="71" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H71" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J71" s="1">
+        <v>20127</v>
+      </c>
+    </row>
+    <row r="72" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H72" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J72" s="1">
+        <v>20131</v>
+      </c>
+    </row>
+    <row r="73" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H73" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J73" s="1">
+        <v>20132</v>
+      </c>
+    </row>
+    <row r="74" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H74" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J74" s="1">
+        <v>20133</v>
+      </c>
+    </row>
+    <row r="75" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H75" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J75" s="1">
+        <v>20134</v>
+      </c>
+    </row>
+    <row r="76" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H76" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J76" s="1">
+        <v>20135</v>
+      </c>
+    </row>
+    <row r="77" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H77" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J77" s="1">
+        <v>20136</v>
+      </c>
+    </row>
+    <row r="78" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H78" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J78" s="1">
+        <v>20137</v>
+      </c>
+    </row>
+    <row r="79" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H79" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J79" s="1">
+        <v>22001</v>
+      </c>
+    </row>
+    <row r="80" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H80" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J80" s="1">
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H81" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J81" s="1">
+        <v>22003</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H84" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J84" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H85" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J85" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H86" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J86" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H87" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J87" s="1">
+        <v>21001</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H88" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J88" s="1">
+        <v>21002</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B90" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J91" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H92" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J92" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H93" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J93" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H94" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J94" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H95" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J95" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H96" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J96" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H97" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J97" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H98" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J98" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H99" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J99" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H100" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J100" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H101" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J101" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H102" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J102" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H103" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J103" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H104" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J104" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B106" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H107" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J107" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H108" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J108" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H109" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J109" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H110" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J110" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H111" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J111" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B113" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H114" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H115" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J115" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H116" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J116" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H117" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J117" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B119" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H120" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J120" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H121" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J121" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B123" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H124" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J124" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H125" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J125" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H126" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J126" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B128" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H129" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J129" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H130" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J130" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H131" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J131" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B133" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H134" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H135" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J135" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H136" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J136" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H137" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J137" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H138" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J138" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H139" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J139" s="1">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C37D8E1-DA5B-4ABC-968B-1F96272F8C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414003BA-6D44-4049-A82E-315D960081D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="30585" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="278">
   <si>
     <t>##var</t>
   </si>
@@ -988,6 +988,62 @@
   </si>
   <si>
     <t>BuffAdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyRecoverNatural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然恢复键数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleRenderResourceCostReason</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扣除原因</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeCounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillFail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillSuccess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放成功</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1358,11 +1414,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="14.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
@@ -2390,485 +2446,568 @@
         <v>21002</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B90" s="1" t="s">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H89" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="J89" s="1">
+        <v>21003</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="G91" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H91" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J90" s="1">
+      <c r="J91" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H91" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J91" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H92" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J92" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H93" s="1" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="J93" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H94" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J94" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H95" s="1" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="J95" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H96" s="1" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="J96" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H97" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J97" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H98" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J98" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H99" s="1" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="J99" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H100" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J100" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H101" s="1" t="s">
-        <v>263</v>
+        <v>188</v>
       </c>
       <c r="J101" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H102" s="1" t="s">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="J102" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H103" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J103" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H104" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J104" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H105" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J104" s="1">
+      <c r="J105" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B106" s="1" t="s">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B107" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="H107" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I107" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J107" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H107" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J107" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H108" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H109" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J109" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J110" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J111" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H112" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="I111" s="1" t="s">
+      <c r="I112" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J111" s="1">
+      <c r="J112" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B113" s="1" t="s">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B114" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G113" s="1" t="s">
+      <c r="G114" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="H114" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I113" s="1" t="s">
+      <c r="I114" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J114" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H114" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J114" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H115" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J115" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J116" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J117" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H118" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="I117" s="1" t="s">
+      <c r="I118" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J117" s="1">
+      <c r="J118" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B119" s="1" t="s">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B120" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G119" s="1" t="s">
+      <c r="G120" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H119" s="1" t="s">
+      <c r="H120" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I119" s="1" t="s">
+      <c r="I120" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J119" s="1">
+      <c r="J120" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H120" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J120" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J121" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H122" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I121" s="1" t="s">
+      <c r="I122" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J122" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B123" s="1" t="s">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B124" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="G123" s="1" t="s">
+      <c r="G124" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="H124" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I123" s="1" t="s">
+      <c r="I124" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J123" s="1">
+      <c r="J124" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H124" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="J124" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H125" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J125" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H126" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J126" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H127" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I126" s="1" t="s">
+      <c r="I127" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J126" s="1">
+      <c r="J127" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B128" s="1" t="s">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B129" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="G128" s="1" t="s">
+      <c r="G129" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="H129" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I128" s="1" t="s">
+      <c r="I129" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J128" s="1">
+      <c r="J129" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H129" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="J129" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J130" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H131" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J131" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H132" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="I132" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="J131" s="1">
+      <c r="J132" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B133" s="1" t="s">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B134" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G133" s="1" t="s">
+      <c r="G134" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H133" s="1" t="s">
+      <c r="H134" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I133" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J133" s="1">
+      <c r="J134" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H134" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J134" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H135" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J135" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H136" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J136" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J137" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J138" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H139" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J139" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H140" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I139" s="1" t="s">
+      <c r="I140" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="J139" s="1">
+      <c r="J140" s="1">
         <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B142" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H143" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H144" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J144" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H145" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J145" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H146" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J146" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H147" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J147" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414003BA-6D44-4049-A82E-315D960081D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F86DA8-28AE-41B4-A84F-74540013F9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="30585" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="310">
   <si>
     <t>##var</t>
   </si>
@@ -959,14 +959,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BeHit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被命中时</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BattleKeyType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1044,6 +1036,142 @@
   </si>
   <si>
     <t>技能释放成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillRemoveMomentType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式结束扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeNextAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff减少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff添加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>决定后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeLastActionGetAll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上次行动前获取的全部清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abnormal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1414,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L147"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2038,7 +2166,7 @@
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H51" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>112</v>
@@ -2093,7 +2221,7 @@
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H56" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>121</v>
@@ -2148,7 +2276,7 @@
     </row>
     <row r="61" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H61" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>130</v>
@@ -2379,7 +2507,7 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B83" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>143</v>
@@ -2448,10 +2576,10 @@
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H89" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J89" s="1">
         <v>21003</v>
@@ -2467,6 +2595,9 @@
       <c r="H91" s="1" t="s">
         <v>183</v>
       </c>
+      <c r="I91" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="J91" s="1">
         <v>1</v>
       </c>
@@ -2475,6 +2606,9 @@
       <c r="H92" s="1" t="s">
         <v>184</v>
       </c>
+      <c r="I92" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="J92" s="1">
         <v>2</v>
       </c>
@@ -2483,6 +2617,9 @@
       <c r="H93" s="1" t="s">
         <v>185</v>
       </c>
+      <c r="I93" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="J93" s="1">
         <v>3</v>
       </c>
@@ -2491,6 +2628,9 @@
       <c r="H94" s="1" t="s">
         <v>232</v>
       </c>
+      <c r="I94" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="J94" s="1">
         <v>4</v>
       </c>
@@ -2499,6 +2639,9 @@
       <c r="H95" s="1" t="s">
         <v>231</v>
       </c>
+      <c r="I95" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="J95" s="1">
         <v>5</v>
       </c>
@@ -2507,6 +2650,9 @@
       <c r="H96" s="1" t="s">
         <v>186</v>
       </c>
+      <c r="I96" s="1" t="s">
+        <v>294</v>
+      </c>
       <c r="J96" s="1">
         <v>6</v>
       </c>
@@ -2515,6 +2661,9 @@
       <c r="H97" s="1" t="s">
         <v>233</v>
       </c>
+      <c r="I97" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="J97" s="1">
         <v>7</v>
       </c>
@@ -2523,6 +2672,9 @@
       <c r="H98" s="1" t="s">
         <v>234</v>
       </c>
+      <c r="I98" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="J98" s="1">
         <v>8</v>
       </c>
@@ -2531,6 +2683,9 @@
       <c r="H99" s="1" t="s">
         <v>235</v>
       </c>
+      <c r="I99" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="J99" s="1">
         <v>9</v>
       </c>
@@ -2539,6 +2694,9 @@
       <c r="H100" s="1" t="s">
         <v>187</v>
       </c>
+      <c r="I100" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="J100" s="1">
         <v>10</v>
       </c>
@@ -2547,13 +2705,19 @@
       <c r="H101" s="1" t="s">
         <v>188</v>
       </c>
+      <c r="I101" s="1" t="s">
+        <v>290</v>
+      </c>
       <c r="J101" s="1">
         <v>11</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H102" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="J102" s="1">
         <v>12</v>
@@ -2563,6 +2727,9 @@
       <c r="H103" s="1" t="s">
         <v>189</v>
       </c>
+      <c r="I103" s="1" t="s">
+        <v>288</v>
+      </c>
       <c r="J103" s="1">
         <v>13</v>
       </c>
@@ -2571,443 +2738,582 @@
       <c r="H104" s="1" t="s">
         <v>190</v>
       </c>
+      <c r="I104" s="1" t="s">
+        <v>287</v>
+      </c>
       <c r="J104" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="J105" s="1">
         <v>15</v>
       </c>
     </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H106" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J106" s="1">
+        <v>16</v>
+      </c>
+    </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B107" s="1" t="s">
+      <c r="H107" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J107" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B109" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="G109" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I107" s="1" t="s">
+      <c r="I109" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J107" s="1">
+      <c r="J109" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H108" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J108" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H109" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J109" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="J110" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J111" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J112" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H113" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J113" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H114" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="I114" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J112" s="1">
+      <c r="J114" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B114" s="1" t="s">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B116" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="G116" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="H116" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I114" s="1" t="s">
+      <c r="I116" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J116" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H115" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J115" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H116" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J116" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J117" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H118" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J118" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H119" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J119" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H120" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="I118" s="1" t="s">
+      <c r="I120" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J118" s="1">
+      <c r="J120" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B120" s="1" t="s">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B122" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G120" s="1" t="s">
+      <c r="G122" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="H122" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I120" s="1" t="s">
+      <c r="I122" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J120" s="1">
+      <c r="J122" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H121" s="1" t="s">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H123" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="I121" s="1" t="s">
+      <c r="I123" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J123" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H122" s="1" t="s">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H124" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I122" s="1" t="s">
+      <c r="I124" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J122" s="1">
+      <c r="J124" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B124" s="1" t="s">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B126" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="G124" s="1" t="s">
+      <c r="G126" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="H126" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I124" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J124" s="1">
+      <c r="J126" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H125" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="J125" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H126" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J126" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J127" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H128" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J128" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H129" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I127" s="1" t="s">
+      <c r="I129" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J127" s="1">
+      <c r="J129" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B129" s="1" t="s">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B131" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="G131" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H131" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I129" s="1" t="s">
+      <c r="I131" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J131" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H130" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="J130" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H131" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J131" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H132" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J132" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H133" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J133" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H134" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J134" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B134" s="1" t="s">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B136" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G134" s="1" t="s">
+      <c r="G136" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="H136" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I134" s="1" t="s">
+      <c r="I136" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J134" s="1">
+      <c r="J136" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H135" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J135" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H136" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J136" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J137" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J138" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H139" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J139" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H140" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J140" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H141" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J141" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H142" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J142" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B142" s="1" t="s">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B144" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H145" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G142" s="1" t="s">
+      <c r="I145" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H146" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J146" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H147" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H142" s="1" t="s">
+      <c r="I147" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J147" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H148" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J148" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H149" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J149" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H151" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I142" s="1" t="s">
+      <c r="I151" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J142" s="1">
+      <c r="J151" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H143" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="J143" s="1">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H152" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J152" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H144" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J144" s="1">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H153" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J153" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H145" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J145" s="1">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H154" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J154" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H146" s="1" t="s">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H155" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I155" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="I146" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="J146" s="1">
+      <c r="J155" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H147" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J147" s="1">
-        <v>5</v>
+    <row r="157" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B157" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H158" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J158" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H159" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J159" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H160" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J160" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F86DA8-28AE-41B4-A84F-74540013F9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532C2056-6EC7-4AA2-ACF6-FA9EC5C7064E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="346">
   <si>
     <t>##var</t>
   </si>
@@ -451,727 +451,872 @@
     <t>DefendInt</t>
   </si>
   <si>
+    <t>DefendPct</t>
+  </si>
+  <si>
+    <t>防百分比变量</t>
+  </si>
+  <si>
+    <t>AllDefendPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前破</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础破</t>
+  </si>
+  <si>
+    <t>BreakInt</t>
+  </si>
+  <si>
+    <t>破整数变量</t>
+  </si>
+  <si>
+    <t>BreakPct</t>
+  </si>
+  <si>
+    <t>破百分比变量</t>
+  </si>
+  <si>
+    <t>AllBreakPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>破外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllGangQiRecPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQiRecInt</t>
+  </si>
+  <si>
+    <t>XuanQiRecPct</t>
+  </si>
+  <si>
+    <t>AllXuanQiRecPct</t>
+  </si>
+  <si>
+    <t>KeyUp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyDown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyLeft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyRight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyMax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>键存储最大值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyMaxEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外键存储值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReducePct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害百分比变动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式伤害直接减免</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KillingDamageReduceInt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecNatural</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQiRecNatural</t>
+  </si>
+  <si>
+    <t>当前刚炁自然恢复值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRedInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRedPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllGangQiRedPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前玄炁自然恢复值</t>
+  </si>
+  <si>
+    <t>玄炁恢复整数变量</t>
+  </si>
+  <si>
+    <t>玄炁恢复百分比变量</t>
+  </si>
+  <si>
+    <t>玄炁恢复外围乘区</t>
+  </si>
+  <si>
+    <t>玄炁消耗整数变量</t>
+  </si>
+  <si>
+    <t>玄炁消耗百分比变量</t>
+  </si>
+  <si>
+    <t>玄炁消耗外围乘区</t>
+  </si>
+  <si>
+    <t>XuanQiRedInt</t>
+  </si>
+  <si>
+    <t>XuanQiRedPct</t>
+  </si>
+  <si>
+    <t>AllXuanQiRedPct</t>
+  </si>
+  <si>
+    <t>扳机时刻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoDesitionAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleMomentType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleSource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Treasure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Natural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageRateFloor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowerKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TechniqueImperialStyle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellFormula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>术杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技御式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法咒式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Direct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>间接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InDirect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleClashType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoubleClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单方面行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeUnderAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterClash</t>
+  </si>
+  <si>
+    <t>ReleaseSkillAction</t>
+  </si>
+  <si>
+    <t>AfterUnderAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffOverlayType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗buff叠加类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dispose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发一下马上结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overlap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduceType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff减少逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少一层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叠加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleKeyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicBreak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicDefend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicClever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyRecoverNatural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然恢复键数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleRenderResourceCostReason</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扣除原因</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeCounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillFail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillSuccess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillRemoveMomentType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式结束扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeNextAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>决定后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeLastActionGetAll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上次行动前获取的全部清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abnormal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextRoundStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个回合开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffAddLayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff添加层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff减少层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff移除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffRemove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduceLayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>防整数变量</t>
-  </si>
-  <si>
-    <t>DefendPct</t>
-  </si>
-  <si>
-    <t>防百分比变量</t>
-  </si>
-  <si>
-    <t>AllDefendPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>防外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前破</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础破</t>
-  </si>
-  <si>
-    <t>BreakInt</t>
-  </si>
-  <si>
-    <t>破整数变量</t>
-  </si>
-  <si>
-    <t>BreakPct</t>
-  </si>
-  <si>
-    <t>破百分比变量</t>
-  </si>
-  <si>
-    <t>AllBreakPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>破外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRecInt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRecPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllGangQiRecPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XuanQiRecInt</t>
-  </si>
-  <si>
-    <t>XuanQiRecPct</t>
-  </si>
-  <si>
-    <t>AllXuanQiRecPct</t>
-  </si>
-  <si>
-    <t>KeyUp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyDown</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyLeft</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyRight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>左键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>右键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyMax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>键存储最大值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyMaxEx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外键存储值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReducePct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害减免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能伤害百分比变动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杀式伤害直接减免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KillingDamageReduceInt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRecNatural</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XuanQiRecNatural</t>
-  </si>
-  <si>
-    <t>当前刚炁自然恢复值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁恢复整数变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁恢复百分比变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁恢复外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRedInt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRedPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllGangQiRedPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁消耗整数变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁消耗百分比变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁消耗外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前玄炁自然恢复值</t>
-  </si>
-  <si>
-    <t>玄炁恢复整数变量</t>
-  </si>
-  <si>
-    <t>玄炁恢复百分比变量</t>
-  </si>
-  <si>
-    <t>玄炁恢复外围乘区</t>
-  </si>
-  <si>
-    <t>玄炁消耗整数变量</t>
-  </si>
-  <si>
-    <t>玄炁消耗百分比变量</t>
-  </si>
-  <si>
-    <t>玄炁消耗外围乘区</t>
-  </si>
-  <si>
-    <t>XuanQiRedInt</t>
-  </si>
-  <si>
-    <t>XuanQiRedPct</t>
-  </si>
-  <si>
-    <t>AllXuanQiRedPct</t>
-  </si>
-  <si>
-    <t>扳机时刻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoDesitionAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeClash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundEnd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffEnd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEnd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleMomentType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleSource</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>来源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeartMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Treasure</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>心法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Natural</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自然</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageRateFloor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>招式类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PowerKilling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArtKilling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TechniqueImperialStyle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpellFormula</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武杀式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>术杀式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技御式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法咒式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Direct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直接伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>间接伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>InDirect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleClashType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SingleAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SingleClash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoubleClash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单方面行动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单向交锋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>双向交锋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeUnderAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterClash</t>
-  </si>
-  <si>
-    <t>ReleaseSkillAction</t>
-  </si>
-  <si>
-    <t>AfterUnderAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffOverlayType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗buff叠加类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dispose</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发一下马上结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cover</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overlap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffReduceType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff减少逻辑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少一层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>One</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllCountPct1Q4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少最后一次叠加后总计数的1/4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllCountPct1Q3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllCountPct1Q2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少最后一次叠加后总计数的1/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少最后一次叠加后总计数的1/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>叠加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleKeyType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicBreak</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicDefend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicClever</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffReduce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffAdd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyRecoverNatural</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自然恢复键数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleRenderResourceCostReason</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扣除原因</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeCounter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseSkillFail</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseSkillSuccess</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能释放失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能释放成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillRemoveMomentType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>招式结束扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下次行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeNextAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个回合结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalculateActionWheel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff减少</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff添加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>决定后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeLastActionGetAll</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上次行动前获取的全部清空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增益</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Abnormal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取技能消耗的获取类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReleaseCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDataGetType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageFinal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostPreview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能预先伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能基础伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能终值伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能预先消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能检测消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamagePreview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyPreview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReleaseKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能预先键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能检测键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能消耗键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因技能获得的刚气该变量偏移值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因技能获得的玄气该变量偏移值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempSkillDamageAddValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempPowerSkillDamageAddValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempArtSkillDamageAddValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时的招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时的武杀式招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时的术杀式招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecoverGangQiBySkillOffset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecoverXuanQiBySkillOffset</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1542,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1550,7 +1695,7 @@
     <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="14.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="30.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
@@ -1649,10 +1794,10 @@
         <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -2166,7 +2311,7 @@
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H51" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>112</v>
@@ -2221,7 +2366,7 @@
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H56" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>121</v>
@@ -2235,7 +2380,7 @@
         <v>122</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="J57" s="1">
         <v>20103</v>
@@ -2243,10 +2388,10 @@
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="J58" s="1">
         <v>20104</v>
@@ -2254,10 +2399,10 @@
     </row>
     <row r="59" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="J59" s="1">
         <v>20105</v>
@@ -2265,10 +2410,10 @@
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="J60" s="1">
         <v>20111</v>
@@ -2276,10 +2421,10 @@
     </row>
     <row r="61" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H61" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J61" s="1">
         <v>20112</v>
@@ -2287,10 +2432,10 @@
     </row>
     <row r="62" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H62" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="J62" s="1">
         <v>20113</v>
@@ -2298,10 +2443,10 @@
     </row>
     <row r="63" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H63" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="J63" s="1">
         <v>20114</v>
@@ -2309,10 +2454,10 @@
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="J64" s="1">
         <v>20115</v>
@@ -2320,10 +2465,10 @@
     </row>
     <row r="65" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H65" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J65" s="1">
         <v>20121</v>
@@ -2331,10 +2476,10 @@
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H66" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J66" s="1">
         <v>20122</v>
@@ -2342,10 +2487,10 @@
     </row>
     <row r="67" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H67" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J67" s="1">
         <v>20123</v>
@@ -2353,10 +2498,10 @@
     </row>
     <row r="68" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H68" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J68" s="1">
         <v>20124</v>
@@ -2364,10 +2509,10 @@
     </row>
     <row r="69" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H69" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J69" s="1">
         <v>20125</v>
@@ -2375,10 +2520,10 @@
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J70" s="1">
         <v>20126</v>
@@ -2386,10 +2531,10 @@
     </row>
     <row r="71" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H71" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J71" s="1">
         <v>20127</v>
@@ -2397,10 +2542,10 @@
     </row>
     <row r="72" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H72" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J72" s="1">
         <v>20131</v>
@@ -2408,10 +2553,10 @@
     </row>
     <row r="73" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H73" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J73" s="1">
         <v>20132</v>
@@ -2419,10 +2564,10 @@
     </row>
     <row r="74" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H74" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J74" s="1">
         <v>20133</v>
@@ -2430,10 +2575,10 @@
     </row>
     <row r="75" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H75" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J75" s="1">
         <v>20134</v>
@@ -2441,10 +2586,10 @@
     </row>
     <row r="76" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H76" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J76" s="1">
         <v>20135</v>
@@ -2452,10 +2597,10 @@
     </row>
     <row r="77" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H77" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J77" s="1">
         <v>20136</v>
@@ -2463,10 +2608,10 @@
     </row>
     <row r="78" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H78" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J78" s="1">
         <v>20137</v>
@@ -2474,10 +2619,10 @@
     </row>
     <row r="79" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H79" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="J79" s="1">
         <v>22001</v>
@@ -2485,10 +2630,10 @@
     </row>
     <row r="80" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H80" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J80" s="1">
         <v>22002</v>
@@ -2496,522 +2641,510 @@
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H81" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J81" s="1">
         <v>22003</v>
       </c>
     </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H82" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J82" s="1">
+        <v>23001</v>
+      </c>
+    </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B83" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="H83" s="1" t="s">
-        <v>143</v>
+        <v>345</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>144</v>
+        <v>337</v>
       </c>
       <c r="J83" s="1">
-        <v>1</v>
+        <v>23002</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>145</v>
+        <v>338</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>148</v>
+        <v>341</v>
       </c>
       <c r="J84" s="1">
-        <v>2</v>
+        <v>23003</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>146</v>
+        <v>339</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="J85" s="1">
-        <v>3</v>
+        <v>23004</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J86" s="1">
+        <v>23005</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B90" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H91" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I91" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J86" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H87" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J87" s="1">
-        <v>21001</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H88" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J88" s="1">
-        <v>21002</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H89" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="J89" s="1">
-        <v>21003</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B91" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="J91" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H92" s="1" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>298</v>
+        <v>148</v>
       </c>
       <c r="J92" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H93" s="1" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="J93" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H94" s="1" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>296</v>
+        <v>151</v>
       </c>
       <c r="J94" s="1">
-        <v>4</v>
+        <v>21001</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H95" s="1" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>295</v>
+        <v>153</v>
       </c>
       <c r="J95" s="1">
-        <v>5</v>
+        <v>21002</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H96" s="1" t="s">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="J96" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H97" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="J97" s="1">
-        <v>7</v>
+        <v>21003</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B98" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="H98" s="1" t="s">
-        <v>234</v>
+        <v>182</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>292</v>
       </c>
       <c r="J98" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H99" s="1" t="s">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>291</v>
       </c>
       <c r="J99" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H100" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="J100" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H101" s="1" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J101" s="1">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H102" s="1" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J102" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H103" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J103" s="1">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H104" s="1" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J104" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="1" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J105" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H106" s="1" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J106" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J107" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H108" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I108" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I107" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="J107" s="1">
-        <v>17</v>
+      <c r="J108" s="1">
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B109" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="H109" s="1" t="s">
-        <v>194</v>
+        <v>305</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>195</v>
+        <v>306</v>
       </c>
       <c r="J109" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>196</v>
+        <v>312</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>205</v>
+        <v>307</v>
       </c>
       <c r="J110" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>200</v>
+        <v>282</v>
       </c>
       <c r="J111" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
-        <v>198</v>
+        <v>309</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>201</v>
+        <v>308</v>
       </c>
       <c r="J112" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H113" s="1" t="s">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>202</v>
+        <v>281</v>
       </c>
       <c r="J113" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H114" s="1" t="s">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="J114" s="1">
-        <v>5</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H115" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J115" s="1">
+        <v>18</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B116" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="H116" s="1" t="s">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="J116" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B118" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J118" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H117" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J117" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H118" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J118" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H119" s="1" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J119" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="J120" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H121" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J121" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H122" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J122" s="1">
         <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B122" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J122" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H123" s="1" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="J123" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B125" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H126" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J126" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H124" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="J124" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B126" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J126" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="J127" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="J128" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="J129" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B131" s="1" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J131" s="1">
         <v>0</v>
@@ -3019,10 +3152,10 @@
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H132" s="1" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="J132" s="1">
         <v>1</v>
@@ -3030,290 +3163,506 @@
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H133" s="1" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="J133" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H134" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="J134" s="1">
-        <v>3</v>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B135" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J135" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B136" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="H136" s="1" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="J136" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="J137" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="J138" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H139" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="J139" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B140" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>235</v>
+      </c>
       <c r="H140" s="1" t="s">
-        <v>251</v>
+        <v>192</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="J140" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H141" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J141" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H142" s="1" t="s">
-        <v>300</v>
+        <v>238</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>301</v>
+        <v>239</v>
       </c>
       <c r="J142" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B144" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J144" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H143" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J143" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J145" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H145" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="J145" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H146" s="1" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="J146" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H147" s="1" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="J147" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H148" s="1" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="J148" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H149" s="1" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="J149" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H150" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J150" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B151" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="H151" s="1" t="s">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>195</v>
+        <v>294</v>
       </c>
       <c r="J151" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B153" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J153" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H152" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="J152" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H153" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="J153" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H154" s="1" t="s">
-        <v>188</v>
+        <v>262</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="J154" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H155" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J155" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H156" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J156" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H157" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J157" s="1">
         <v>4</v>
-      </c>
-    </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B157" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I157" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J157" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H158" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J158" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B160" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H161" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J161" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H162" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J162" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H163" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J163" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H164" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J164" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H165" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I165" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="I158" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="J158" s="1">
+      <c r="J165" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B167" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H168" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J168" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H159" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J159" s="1">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H169" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J169" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H160" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J160" s="1">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H170" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J170" s="1">
         <v>3</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B172" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H173" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J173" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H174" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="J174" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H175" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J175" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H176" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J176" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H177" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J177" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H178" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J178" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H179" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J179" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H180" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J180" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H181" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J181" s="1">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532C2056-6EC7-4AA2-ACF6-FA9EC5C7064E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC34259-CBD5-4328-BC03-867E42F8EF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2205" yWindow="2205" windowWidth="35565" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -417,906 +417,907 @@
     <t>基础巧</t>
   </si>
   <si>
+    <t>巧整数变量</t>
+  </si>
+  <si>
+    <t>CleverPct</t>
+  </si>
+  <si>
+    <t>巧百分比变量</t>
+  </si>
+  <si>
+    <t>AllCleverPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>巧外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defend</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前防</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础防</t>
+  </si>
+  <si>
+    <t>DefendInt</t>
+  </si>
+  <si>
+    <t>DefendPct</t>
+  </si>
+  <si>
+    <t>防百分比变量</t>
+  </si>
+  <si>
+    <t>AllDefendPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前破</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础破</t>
+  </si>
+  <si>
+    <t>BreakInt</t>
+  </si>
+  <si>
+    <t>破整数变量</t>
+  </si>
+  <si>
+    <t>BreakPct</t>
+  </si>
+  <si>
+    <t>破百分比变量</t>
+  </si>
+  <si>
+    <t>AllBreakPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>破外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllGangQiRecPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQiRecInt</t>
+  </si>
+  <si>
+    <t>XuanQiRecPct</t>
+  </si>
+  <si>
+    <t>AllXuanQiRecPct</t>
+  </si>
+  <si>
+    <t>KeyUp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyDown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyLeft</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyRight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyMax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>键存储最大值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyMaxEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外键存储值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReducePct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害百分比变动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式伤害直接减免</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KillingDamageReduceInt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRecNatural</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQiRecNatural</t>
+  </si>
+  <si>
+    <t>当前刚炁自然恢复值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁恢复外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRedInt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiRedPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllGangQiRedPct</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗整数变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗百分比变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗外围乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前玄炁自然恢复值</t>
+  </si>
+  <si>
+    <t>玄炁恢复整数变量</t>
+  </si>
+  <si>
+    <t>玄炁恢复百分比变量</t>
+  </si>
+  <si>
+    <t>玄炁恢复外围乘区</t>
+  </si>
+  <si>
+    <t>玄炁消耗整数变量</t>
+  </si>
+  <si>
+    <t>玄炁消耗百分比变量</t>
+  </si>
+  <si>
+    <t>玄炁消耗外围乘区</t>
+  </si>
+  <si>
+    <t>XuanQiRedInt</t>
+  </si>
+  <si>
+    <t>XuanQiRedPct</t>
+  </si>
+  <si>
+    <t>AllXuanQiRedPct</t>
+  </si>
+  <si>
+    <t>扳机时刻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoDesitionAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleMomentType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleSource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartMethod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Treasure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Natural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageRateFloor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowerKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TechniqueImperialStyle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellFormula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>术杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技御式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法咒式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Direct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>间接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InDirect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleClashType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoubleClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单方面行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeUnderAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterClash</t>
+  </si>
+  <si>
+    <t>ReleaseSkillAction</t>
+  </si>
+  <si>
+    <t>AfterUnderAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffOverlayType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗buff叠加类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dispose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发一下马上结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overlap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduceType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff减少逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少一层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllCountPct1Q2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少最后一次叠加后总计数的1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叠加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleKeyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicBreak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicDefend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicClever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyRecoverNatural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然恢复键数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleRenderResourceCostReason</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扣除原因</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeCounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillFail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseSkillSuccess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillRemoveMomentType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式结束扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeNextAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>决定后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeLastActionGetAll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上次行动前获取的全部清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abnormal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextRoundStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个回合开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffAddLayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff添加层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff减少层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff移除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffRemove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduceLayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防整数变量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelEnd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取技能消耗的获取类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReleaseCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDataGetType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageFinal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostPreview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能预先伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能基础伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能终值伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能预先消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能检测消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能释放消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamagePreview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyPreview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReleaseKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能预先键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能检测键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能消耗键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因技能获得的刚气该变量偏移值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因技能获得的玄气该变量偏移值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempSkillDamageAddValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempPowerSkillDamageAddValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempArtSkillDamageAddValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时的招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时的武杀式招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时的术杀式招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecoverGangQiBySkillOffset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecoverXuanQiBySkillOffset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CleverInt</t>
-  </si>
-  <si>
-    <t>巧整数变量</t>
-  </si>
-  <si>
-    <t>CleverPct</t>
-  </si>
-  <si>
-    <t>巧百分比变量</t>
-  </si>
-  <si>
-    <t>AllCleverPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>巧外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defend</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前防</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础防</t>
-  </si>
-  <si>
-    <t>DefendInt</t>
-  </si>
-  <si>
-    <t>DefendPct</t>
-  </si>
-  <si>
-    <t>防百分比变量</t>
-  </si>
-  <si>
-    <t>AllDefendPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>防外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前破</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础破</t>
-  </si>
-  <si>
-    <t>BreakInt</t>
-  </si>
-  <si>
-    <t>破整数变量</t>
-  </si>
-  <si>
-    <t>BreakPct</t>
-  </si>
-  <si>
-    <t>破百分比变量</t>
-  </si>
-  <si>
-    <t>AllBreakPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>破外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRecInt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRecPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllGangQiRecPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XuanQiRecInt</t>
-  </si>
-  <si>
-    <t>XuanQiRecPct</t>
-  </si>
-  <si>
-    <t>AllXuanQiRecPct</t>
-  </si>
-  <si>
-    <t>KeyUp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyDown</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyLeft</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyRight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>左键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>右键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyMax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>键存储最大值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyMaxEx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外键存储值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReducePct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害减免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能伤害百分比变动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杀式伤害直接减免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KillingDamageReduceInt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRecNatural</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XuanQiRecNatural</t>
-  </si>
-  <si>
-    <t>当前刚炁自然恢复值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁恢复整数变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁恢复百分比变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁恢复外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRedInt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GangQiRedPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllGangQiRedPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁消耗整数变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁消耗百分比变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁消耗外围乘区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前玄炁自然恢复值</t>
-  </si>
-  <si>
-    <t>玄炁恢复整数变量</t>
-  </si>
-  <si>
-    <t>玄炁恢复百分比变量</t>
-  </si>
-  <si>
-    <t>玄炁恢复外围乘区</t>
-  </si>
-  <si>
-    <t>玄炁消耗整数变量</t>
-  </si>
-  <si>
-    <t>玄炁消耗百分比变量</t>
-  </si>
-  <si>
-    <t>玄炁消耗外围乘区</t>
-  </si>
-  <si>
-    <t>XuanQiRedInt</t>
-  </si>
-  <si>
-    <t>XuanQiRedPct</t>
-  </si>
-  <si>
-    <t>AllXuanQiRedPct</t>
-  </si>
-  <si>
-    <t>扳机时刻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoDesitionAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeClash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundEnd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEnd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleMomentType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleSource</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>来源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeartMethod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Treasure</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>心法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Natural</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自然</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageRateFloor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>招式类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PowerKilling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArtKilling</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TechniqueImperialStyle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpellFormula</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武杀式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>术杀式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技御式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法咒式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Direct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直接伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>间接伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>InDirect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleClashType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SingleAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SingleClash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoubleClash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单方面行动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单向交锋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>双向交锋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeUnderAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterClash</t>
-  </si>
-  <si>
-    <t>ReleaseSkillAction</t>
-  </si>
-  <si>
-    <t>AfterUnderAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffOverlayType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗buff叠加类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dispose</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发一下马上结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cover</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overlap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffReduceType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff减少逻辑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少一层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>One</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllCountPct1Q4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少最后一次叠加后总计数的1/4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllCountPct1Q3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllCountPct1Q2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少最后一次叠加后总计数的1/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>减少最后一次叠加后总计数的1/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>叠加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleKeyType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicBreak</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicDefend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicClever</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyRecoverNatural</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自然恢复键数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleRenderResourceCostReason</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扣除原因</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeCounter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseSkillFail</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseSkillSuccess</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能释放失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能释放成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillRemoveMomentType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>招式结束扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下次行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeNextAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个回合结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalculateActionWheel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>决定后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeLastActionGetAll</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上次行动前获取的全部清空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增益</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Abnormal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Special</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NextRoundStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下个回合开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffAddLayer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff添加层数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff减少层数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff移除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffRemove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffReduceLayer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防整数变量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelEnd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取技能消耗的获取类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReleaseCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDataGetType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageFinal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageBase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CheckCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CostPreview</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能预先伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能基础伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能终值伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能预先消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能检测消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能释放消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamagePreview</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyPreview</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CheckKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReleaseKey</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能预先键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能检测键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能消耗键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>因技能获得的刚气该变量偏移值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>因技能获得的玄气该变量偏移值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TempSkillDamageAddValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TempPowerSkillDamageAddValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TempArtSkillDamageAddValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>临时的招式威力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>临时的武杀式招式威力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>临时的术杀式招式威力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecoverGangQiBySkillOffset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecoverXuanQiBySkillOffset</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1794,10 +1795,10 @@
         <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -2311,7 +2312,7 @@
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H51" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>112</v>
@@ -2322,10 +2323,10 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="J52" s="1">
         <v>20093</v>
@@ -2333,10 +2334,10 @@
     </row>
     <row r="53" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="J53" s="1">
         <v>20094</v>
@@ -2344,10 +2345,10 @@
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H54" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="J54" s="1">
         <v>20095</v>
@@ -2355,10 +2356,10 @@
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="J55" s="1">
         <v>20101</v>
@@ -2366,10 +2367,10 @@
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H56" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J56" s="1">
         <v>20102</v>
@@ -2377,10 +2378,10 @@
     </row>
     <row r="57" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H57" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J57" s="1">
         <v>20103</v>
@@ -2388,10 +2389,10 @@
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="J58" s="1">
         <v>20104</v>
@@ -2399,10 +2400,10 @@
     </row>
     <row r="59" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H59" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="J59" s="1">
         <v>20105</v>
@@ -2410,10 +2411,10 @@
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H60" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="J60" s="1">
         <v>20111</v>
@@ -2421,10 +2422,10 @@
     </row>
     <row r="61" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H61" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J61" s="1">
         <v>20112</v>
@@ -2432,10 +2433,10 @@
     </row>
     <row r="62" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H62" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="J62" s="1">
         <v>20113</v>
@@ -2443,10 +2444,10 @@
     </row>
     <row r="63" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H63" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="J63" s="1">
         <v>20114</v>
@@ -2454,10 +2455,10 @@
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="J64" s="1">
         <v>20115</v>
@@ -2465,10 +2466,10 @@
     </row>
     <row r="65" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H65" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J65" s="1">
         <v>20121</v>
@@ -2476,10 +2477,10 @@
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H66" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J66" s="1">
         <v>20122</v>
@@ -2487,10 +2488,10 @@
     </row>
     <row r="67" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H67" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J67" s="1">
         <v>20123</v>
@@ -2498,10 +2499,10 @@
     </row>
     <row r="68" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H68" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J68" s="1">
         <v>20124</v>
@@ -2509,10 +2510,10 @@
     </row>
     <row r="69" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H69" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J69" s="1">
         <v>20125</v>
@@ -2520,10 +2521,10 @@
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J70" s="1">
         <v>20126</v>
@@ -2531,10 +2532,10 @@
     </row>
     <row r="71" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H71" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J71" s="1">
         <v>20127</v>
@@ -2542,10 +2543,10 @@
     </row>
     <row r="72" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H72" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J72" s="1">
         <v>20131</v>
@@ -2553,10 +2554,10 @@
     </row>
     <row r="73" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H73" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J73" s="1">
         <v>20132</v>
@@ -2564,10 +2565,10 @@
     </row>
     <row r="74" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H74" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J74" s="1">
         <v>20133</v>
@@ -2575,10 +2576,10 @@
     </row>
     <row r="75" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H75" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J75" s="1">
         <v>20134</v>
@@ -2586,10 +2587,10 @@
     </row>
     <row r="76" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H76" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J76" s="1">
         <v>20135</v>
@@ -2597,10 +2598,10 @@
     </row>
     <row r="77" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H77" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J77" s="1">
         <v>20136</v>
@@ -2608,10 +2609,10 @@
     </row>
     <row r="78" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H78" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J78" s="1">
         <v>20137</v>
@@ -2619,10 +2620,10 @@
     </row>
     <row r="79" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H79" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="J79" s="1">
         <v>22001</v>
@@ -2630,10 +2631,10 @@
     </row>
     <row r="80" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H80" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J80" s="1">
         <v>22002</v>
@@ -2641,10 +2642,10 @@
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H81" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J81" s="1">
         <v>22003</v>
@@ -2652,10 +2653,10 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J82" s="1">
         <v>23001</v>
@@ -2663,10 +2664,10 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H83" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J83" s="1">
         <v>23002</v>
@@ -2674,10 +2675,10 @@
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J84" s="1">
         <v>23003</v>
@@ -2685,10 +2686,10 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J85" s="1">
         <v>23004</v>
@@ -2696,10 +2697,10 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J86" s="1">
         <v>23005</v>
@@ -2707,13 +2708,13 @@
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B90" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H90" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I90" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="J90" s="1">
         <v>1</v>
@@ -2721,10 +2722,10 @@
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H91" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J91" s="1">
         <v>2</v>
@@ -2732,10 +2733,10 @@
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H92" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J92" s="1">
         <v>3</v>
@@ -2743,10 +2744,10 @@
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H93" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J93" s="1">
         <v>4</v>
@@ -2754,10 +2755,10 @@
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H94" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="J94" s="1">
         <v>21001</v>
@@ -2765,10 +2766,10 @@
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H95" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="J95" s="1">
         <v>21002</v>
@@ -2776,10 +2777,10 @@
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H96" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="J96" s="1">
         <v>21003</v>
@@ -2787,16 +2788,16 @@
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G98" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H98" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="I98" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J98" s="1">
         <v>1</v>
@@ -2804,10 +2805,10 @@
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H99" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J99" s="1">
         <v>2</v>
@@ -2815,10 +2816,10 @@
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H100" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J100" s="1">
         <v>3</v>
@@ -2826,10 +2827,10 @@
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H101" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J101" s="1">
         <v>4</v>
@@ -2837,10 +2838,10 @@
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H102" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J102" s="1">
         <v>5</v>
@@ -2848,10 +2849,10 @@
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H103" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J103" s="1">
         <v>6</v>
@@ -2859,10 +2860,10 @@
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H104" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J104" s="1">
         <v>7</v>
@@ -2870,10 +2871,10 @@
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J105" s="1">
         <v>8</v>
@@ -2881,10 +2882,10 @@
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H106" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J106" s="1">
         <v>9</v>
@@ -2892,10 +2893,10 @@
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J107" s="1">
         <v>10</v>
@@ -2903,10 +2904,10 @@
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H108" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J108" s="1">
         <v>11</v>
@@ -2914,10 +2915,10 @@
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H109" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="J109" s="1">
         <v>12</v>
@@ -2925,10 +2926,10 @@
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J110" s="1">
         <v>13</v>
@@ -2936,10 +2937,10 @@
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J111" s="1">
         <v>14</v>
@@ -2947,10 +2948,10 @@
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J112" s="1">
         <v>15</v>
@@ -2958,10 +2959,10 @@
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H113" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J113" s="1">
         <v>16</v>
@@ -2969,10 +2970,10 @@
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H114" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I114" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="J114" s="1">
         <v>17</v>
@@ -2980,10 +2981,10 @@
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H115" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J115" s="1">
         <v>18</v>
@@ -2991,10 +2992,10 @@
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="J116" s="1">
         <v>19</v>
@@ -3002,16 +3003,16 @@
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B118" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G118" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="H118" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="I118" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J118" s="1">
         <v>0</v>
@@ -3019,10 +3020,10 @@
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H119" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J119" s="1">
         <v>1</v>
@@ -3030,10 +3031,10 @@
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J120" s="1">
         <v>2</v>
@@ -3041,10 +3042,10 @@
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J121" s="1">
         <v>3</v>
@@ -3052,10 +3053,10 @@
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H122" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J122" s="1">
         <v>4</v>
@@ -3063,10 +3064,10 @@
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H123" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I123" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="J123" s="1">
         <v>5</v>
@@ -3074,16 +3075,16 @@
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B125" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G125" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G125" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="H125" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I125" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J125" s="1">
         <v>0</v>
@@ -3091,10 +3092,10 @@
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H126" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J126" s="1">
         <v>1</v>
@@ -3102,10 +3103,10 @@
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J127" s="1">
         <v>2</v>
@@ -3113,10 +3114,10 @@
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J128" s="1">
         <v>3</v>
@@ -3124,10 +3125,10 @@
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J129" s="1">
         <v>4</v>
@@ -3135,16 +3136,16 @@
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B131" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H131" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I131" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J131" s="1">
         <v>0</v>
@@ -3152,10 +3153,10 @@
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H132" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J132" s="1">
         <v>1</v>
@@ -3163,10 +3164,10 @@
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H133" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J133" s="1">
         <v>2</v>
@@ -3174,16 +3175,16 @@
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B135" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G135" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G135" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="H135" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I135" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J135" s="1">
         <v>0</v>
@@ -3191,10 +3192,10 @@
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H136" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J136" s="1">
         <v>1</v>
@@ -3202,10 +3203,10 @@
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J137" s="1">
         <v>2</v>
@@ -3213,10 +3214,10 @@
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J138" s="1">
         <v>3</v>
@@ -3224,16 +3225,16 @@
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B140" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G140" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="G140" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="H140" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I140" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J140" s="1">
         <v>0</v>
@@ -3241,10 +3242,10 @@
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H141" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I141" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="J141" s="1">
         <v>1</v>
@@ -3252,10 +3253,10 @@
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H142" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I142" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="J142" s="1">
         <v>2</v>
@@ -3263,10 +3264,10 @@
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H143" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J143" s="1">
         <v>3</v>
@@ -3274,16 +3275,16 @@
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B145" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G145" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="G145" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="H145" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I145" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J145" s="1">
         <v>0</v>
@@ -3291,10 +3292,10 @@
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H146" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -3302,10 +3303,10 @@
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H147" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I147" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="J147" s="1">
         <v>2</v>
@@ -3313,10 +3314,10 @@
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H148" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I148" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="J148" s="1">
         <v>3</v>
@@ -3324,10 +3325,10 @@
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H149" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J149" s="1">
         <v>4</v>
@@ -3335,10 +3336,10 @@
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H150" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J150" s="1">
         <v>5</v>
@@ -3346,10 +3347,10 @@
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H151" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="I151" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="J151" s="1">
         <v>6</v>
@@ -3357,16 +3358,16 @@
     </row>
     <row r="153" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B153" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G153" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="G153" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="H153" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I153" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J153" s="1">
         <v>0</v>
@@ -3374,10 +3375,10 @@
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H154" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J154" s="1">
         <v>1</v>
@@ -3385,10 +3386,10 @@
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H155" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J155" s="1">
         <v>2</v>
@@ -3396,10 +3397,10 @@
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H156" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J156" s="1">
         <v>3</v>
@@ -3407,10 +3408,10 @@
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H157" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J157" s="1">
         <v>4</v>
@@ -3418,10 +3419,10 @@
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H158" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J158" s="1">
         <v>5</v>
@@ -3429,16 +3430,16 @@
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B160" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G160" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G160" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="H160" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J160" s="1">
         <v>0</v>
@@ -3446,10 +3447,10 @@
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H161" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J161" s="1">
         <v>1</v>
@@ -3457,10 +3458,10 @@
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H162" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J162" s="1">
         <v>2</v>
@@ -3468,10 +3469,10 @@
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H163" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J163" s="1">
         <v>3</v>
@@ -3479,10 +3480,10 @@
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H164" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J164" s="1">
         <v>4</v>
@@ -3490,10 +3491,10 @@
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H165" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I165" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="J165" s="1">
         <v>5</v>
@@ -3501,16 +3502,16 @@
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B167" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G167" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="G167" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="H167" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I167" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I167" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J167" s="1">
         <v>0</v>
@@ -3518,10 +3519,10 @@
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H168" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I168" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="I168" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="J168" s="1">
         <v>1</v>
@@ -3529,10 +3530,10 @@
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H169" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I169" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="I169" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="J169" s="1">
         <v>2</v>
@@ -3540,10 +3541,10 @@
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H170" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J170" s="1">
         <v>3</v>
@@ -3551,16 +3552,16 @@
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B172" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H172" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I172" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I172" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J172" s="1">
         <v>0</v>
@@ -3568,10 +3569,10 @@
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H173" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J173" s="1">
         <v>1</v>
@@ -3579,10 +3580,10 @@
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H174" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J174" s="1">
         <v>2</v>
@@ -3590,10 +3591,10 @@
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H175" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J175" s="1">
         <v>3</v>
@@ -3601,10 +3602,10 @@
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H176" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J176" s="1">
         <v>4</v>
@@ -3612,10 +3613,10 @@
     </row>
     <row r="177" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H177" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J177" s="1">
         <v>5</v>
@@ -3623,10 +3624,10 @@
     </row>
     <row r="178" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H178" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J178" s="1">
         <v>6</v>
@@ -3634,10 +3635,10 @@
     </row>
     <row r="179" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H179" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J179" s="1">
         <v>7</v>
@@ -3645,10 +3646,10 @@
     </row>
     <row r="180" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H180" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J180" s="1">
         <v>8</v>
@@ -3656,10 +3657,10 @@
     </row>
     <row r="181" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H181" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J181" s="1">
         <v>9</v>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC34259-CBD5-4328-BC03-867E42F8EF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83AEEF9-95F1-4E75-B801-45B8E430AA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2205" yWindow="2205" windowWidth="35565" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="348">
   <si>
     <t>##var</t>
   </si>
@@ -1233,10 +1233,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>技能终值伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技能预先消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1318,6 +1314,18 @@
   </si>
   <si>
     <t>CleverInt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能交锋伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能最终伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1688,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2323,7 +2331,7 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>113</v>
@@ -2653,10 +2661,10 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J82" s="1">
         <v>23001</v>
@@ -2664,10 +2672,10 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H83" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J83" s="1">
         <v>23002</v>
@@ -2675,10 +2683,10 @@
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J84" s="1">
         <v>23003</v>
@@ -2686,10 +2694,10 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J85" s="1">
         <v>23004</v>
@@ -2697,10 +2705,10 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J86" s="1">
         <v>23005</v>
@@ -3572,7 +3580,7 @@
         <v>321</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J173" s="1">
         <v>1</v>
@@ -3583,7 +3591,7 @@
         <v>320</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J174" s="1">
         <v>2</v>
@@ -3594,7 +3602,7 @@
         <v>316</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J175" s="1">
         <v>3</v>
@@ -3602,7 +3610,7 @@
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H176" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>322</v>
@@ -3624,10 +3632,10 @@
     </row>
     <row r="178" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H178" s="1" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="J178" s="1">
         <v>6</v>
@@ -3635,10 +3643,10 @@
     </row>
     <row r="179" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H179" s="1" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="J179" s="1">
         <v>7</v>
@@ -3646,10 +3654,10 @@
     </row>
     <row r="180" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H180" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J180" s="1">
         <v>8</v>
@@ -3657,13 +3665,24 @@
     </row>
     <row r="181" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H181" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J181" s="1">
         <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H182" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J182" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83AEEF9-95F1-4E75-B801-45B8E430AA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2099ADD-F797-41B2-A097-9F32A152A4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="356">
   <si>
     <t>##var</t>
   </si>
@@ -1209,10 +1220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DamageFinal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DamageBase</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1317,15 +1324,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>技能交锋伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageClash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能最终伤害</t>
+    <t>英雄类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeroVariety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Person</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weird</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ghost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageCurr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能当前伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1696,7 +1739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L182"/>
+  <dimension ref="A1:L187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2331,7 +2374,7 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>113</v>
@@ -2661,10 +2704,10 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J82" s="1">
         <v>23001</v>
@@ -2672,10 +2715,10 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H83" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J83" s="1">
         <v>23002</v>
@@ -2683,10 +2726,10 @@
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J84" s="1">
         <v>23003</v>
@@ -2694,10 +2737,10 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J85" s="1">
         <v>23004</v>
@@ -2705,10 +2748,10 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J86" s="1">
         <v>23005</v>
@@ -3577,10 +3620,10 @@
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H173" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J173" s="1">
         <v>1</v>
@@ -3588,10 +3631,10 @@
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H174" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J174" s="1">
         <v>2</v>
@@ -3602,7 +3645,7 @@
         <v>316</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J175" s="1">
         <v>3</v>
@@ -3610,49 +3653,49 @@
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H176" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J176" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H177" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J177" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H178" s="1" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J178" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H179" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="J179" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H180" s="1" t="s">
         <v>328</v>
       </c>
@@ -3663,7 +3706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H181" s="1" t="s">
         <v>329</v>
       </c>
@@ -3674,15 +3717,65 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H182" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I182" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="J182" s="1">
-        <v>10</v>
+    <row r="183" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H184" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J184" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H185" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J185" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H186" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="J186" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H187" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="J187" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2099ADD-F797-41B2-A097-9F32A152A4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9738F39D-6890-4C03-AE6C-801F27512433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="378">
   <si>
     <t>##var</t>
   </si>
@@ -1068,10 +1068,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>息开始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技能结束</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1369,6 +1365,98 @@
   </si>
   <si>
     <t>技能当前伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeatherType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天气类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChronoType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时辰类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早晨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunrise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Morning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Night</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己息开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EveryActionWheelStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每息开始</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1739,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L187"/>
+  <dimension ref="A1:L200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2374,7 +2462,7 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>113</v>
@@ -2432,7 +2520,7 @@
         <v>121</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J57" s="1">
         <v>20103</v>
@@ -2704,10 +2792,10 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J82" s="1">
         <v>23001</v>
@@ -2715,10 +2803,10 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H83" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J83" s="1">
         <v>23002</v>
@@ -2726,10 +2814,10 @@
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J84" s="1">
         <v>23003</v>
@@ -2737,10 +2825,10 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J85" s="1">
         <v>23004</v>
@@ -2748,19 +2836,30 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J86" s="1">
         <v>23005</v>
       </c>
     </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B89" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J89" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B90" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="H90" s="1" t="s">
         <v>141</v>
       </c>
@@ -2848,7 +2947,7 @@
         <v>181</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J98" s="1">
         <v>1</v>
@@ -2859,7 +2958,7 @@
         <v>182</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J99" s="1">
         <v>2</v>
@@ -2870,7 +2969,7 @@
         <v>183</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J100" s="1">
         <v>3</v>
@@ -2881,7 +2980,7 @@
         <v>229</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J101" s="1">
         <v>4</v>
@@ -2892,7 +2991,7 @@
         <v>228</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J102" s="1">
         <v>5</v>
@@ -2903,7 +3002,7 @@
         <v>184</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J103" s="1">
         <v>6</v>
@@ -2914,7 +3013,7 @@
         <v>230</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J104" s="1">
         <v>7</v>
@@ -2925,7 +3024,7 @@
         <v>231</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J105" s="1">
         <v>8</v>
@@ -2936,7 +3035,7 @@
         <v>232</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J106" s="1">
         <v>9</v>
@@ -2958,7 +3057,7 @@
         <v>186</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J108" s="1">
         <v>11</v>
@@ -2966,10 +3065,10 @@
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H109" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="J109" s="1">
         <v>12</v>
@@ -2977,10 +3076,10 @@
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J110" s="1">
         <v>13</v>
@@ -2991,7 +3090,7 @@
         <v>187</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J111" s="1">
         <v>14</v>
@@ -2999,10 +3098,10 @@
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J112" s="1">
         <v>15</v>
@@ -3013,7 +3112,7 @@
         <v>271</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>280</v>
+        <v>375</v>
       </c>
       <c r="J113" s="1">
         <v>16</v>
@@ -3032,10 +3131,10 @@
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H115" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J115" s="1">
         <v>18</v>
@@ -3043,590 +3142,590 @@
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="J116" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B118" s="1" t="s">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H117" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J117" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B119" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="G119" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="H119" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I118" s="1" t="s">
+      <c r="I119" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J118" s="1">
+      <c r="J119" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H119" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="J119" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J120" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J121" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H122" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J122" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H123" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J123" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H124" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="I123" s="1" t="s">
+      <c r="I124" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J123" s="1">
+      <c r="J124" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B125" s="1" t="s">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B126" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="G126" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="H126" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I125" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J125" s="1">
+      <c r="J126" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H126" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J126" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J127" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J128" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J129" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H130" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I129" s="1" t="s">
+      <c r="I130" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J130" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B131" s="1" t="s">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B132" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G131" s="1" t="s">
+      <c r="G132" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="H132" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="I132" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J131" s="1">
+      <c r="J132" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H132" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="J132" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H133" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J133" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H134" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I133" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J133" s="1">
+      <c r="J134" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B135" s="1" t="s">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B136" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="G135" s="1" t="s">
+      <c r="G136" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="H135" s="1" t="s">
+      <c r="H136" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I135" s="1" t="s">
+      <c r="I136" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J135" s="1">
+      <c r="J136" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H136" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J136" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J137" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J138" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H139" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="I139" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J139" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B140" s="1" t="s">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B141" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="G140" s="1" t="s">
+      <c r="G141" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="H140" s="1" t="s">
+      <c r="H141" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="I141" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J140" s="1">
+      <c r="J141" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H141" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J141" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H142" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J142" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H143" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J143" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H144" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="I143" s="1" t="s">
+      <c r="I144" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="J143" s="1">
+      <c r="J144" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B145" s="1" t="s">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G145" s="1" t="s">
+      <c r="G146" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H145" s="1" t="s">
+      <c r="H146" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I145" s="1" t="s">
+      <c r="I146" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J145" s="1">
+      <c r="J146" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H146" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="J146" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H147" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J147" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H148" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J148" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H149" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J149" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H150" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J150" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H151" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J151" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H152" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I152" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I151" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="J151" s="1">
+      <c r="J152" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B153" s="1" t="s">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B154" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G153" s="1" t="s">
+      <c r="G154" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="H154" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I153" s="1" t="s">
+      <c r="I154" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J153" s="1">
+      <c r="J154" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H154" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="J154" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H155" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J155" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H156" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J156" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H157" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J157" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H158" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J158" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H159" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="I158" s="1" t="s">
+      <c r="I159" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J158" s="1">
+      <c r="J159" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B160" s="1" t="s">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B161" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G160" s="1" t="s">
+      <c r="G161" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H160" s="1" t="s">
+      <c r="H161" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="I161" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J161" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H161" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J161" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H162" s="1" t="s">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J162" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H163" s="1" t="s">
-        <v>186</v>
+        <v>276</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J163" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H164" s="1" t="s">
-        <v>261</v>
+        <v>186</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="J164" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H165" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="J165" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H166" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I166" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="I165" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="J165" s="1">
+      <c r="J166" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B167" s="1" t="s">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B168" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G168" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="G167" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="H167" s="1" t="s">
+      <c r="H168" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I167" s="1" t="s">
+      <c r="I168" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J167" s="1">
+      <c r="J168" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H168" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I168" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="J168" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H169" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J169" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H170" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I170" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J170" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H171" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="J170" s="1">
+      <c r="I171" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J171" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B172" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="H172" s="1" t="s">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B173" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="H173" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I172" s="1" t="s">
+      <c r="I173" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J172" s="1">
+      <c r="J173" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H173" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="J173" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.2">
@@ -3634,147 +3733,280 @@
         <v>319</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J174" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H175" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J175" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H176" s="1" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J176" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H177" s="1" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J177" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H178" s="1" t="s">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>355</v>
+        <v>321</v>
       </c>
       <c r="J178" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H179" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="J179" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H180" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J180" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H181" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J181" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H182" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="J182" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B183" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="G183" s="1" t="s">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B184" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="H183" s="1" t="s">
+      <c r="G184" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H184" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I183" s="1" t="s">
+      <c r="I184" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J183" s="1">
+      <c r="J184" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H184" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="I184" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="J184" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H185" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J185" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H186" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J186" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H187" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J187" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H188" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I188" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="I187" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="J187" s="1">
+      <c r="J188" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B190" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J190" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H191" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="J191" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H192" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="J192" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H193" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J193" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H194" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J194" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B196" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J196" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H197" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J197" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H198" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J198" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H199" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="J199" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H200" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="J200" s="1">
         <v>4</v>
       </c>
     </row>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9738F39D-6890-4C03-AE6C-801F27512433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EB47ED-BDF2-47E0-886D-F36D351DC835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="441">
   <si>
     <t>##var</t>
   </si>
@@ -1284,18 +1284,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TempSkillDamageAddValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TempPowerSkillDamageAddValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TempArtSkillDamageAddValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>临时的招式威力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1457,6 +1445,269 @@
   </si>
   <si>
     <t>每息开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerBuffMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接触发buff扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffMechanism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotBeAddAbnormalBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法被施加异常状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotBeActionTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法成为被行动的目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破提升效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakAddPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefendAddPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防提升效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CleverAddPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巧提升效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速提升效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeedAddPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TechAddPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技提升效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowerAddPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力提升效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LockUpKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封锁上键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LockDownKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LockLeftKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LockRightKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封锁下键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封锁左键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封锁右键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回避和盲目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffReduceDamage1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mockery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘲讽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotBeAddGainBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法被施加增益状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotEffectGainBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法生效增益Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotEffectAbnormalBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法生效异常Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotEffectSpecialBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法生效特殊Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempSkillAddWellyRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempPowerSkillAddWellyRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempArtSkillAddWellyRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法直接清除异常状态</t>
+  </si>
+  <si>
+    <t>NotDirectRemoveAbnormalBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改变键的原因</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NaturalRecover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Init</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanUseNiShaSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可使用猊煞变派系招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleUnitTransformState</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>禽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeKeyReason</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1827,7 +2078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1836,7 +2087,7 @@
     <col min="4" max="5" width="14.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="35.25" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
@@ -2330,1199 +2581,1204 @@
     </row>
     <row r="40" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H40" s="1" t="s">
-        <v>90</v>
+        <v>393</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>91</v>
+        <v>394</v>
       </c>
       <c r="J40" s="1">
-        <v>20071</v>
+        <v>20066</v>
       </c>
     </row>
     <row r="41" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H41" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J41" s="1">
-        <v>20072</v>
+        <v>20071</v>
       </c>
     </row>
     <row r="42" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H42" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J42" s="1">
-        <v>20073</v>
+        <v>20072</v>
       </c>
     </row>
     <row r="43" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H43" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J43" s="1">
-        <v>20074</v>
+        <v>20073</v>
       </c>
     </row>
     <row r="44" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H44" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J44" s="1">
-        <v>20075</v>
+        <v>20074</v>
       </c>
     </row>
     <row r="45" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H45" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J45" s="1">
-        <v>20081</v>
+        <v>20075</v>
       </c>
     </row>
     <row r="46" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H46" s="1" t="s">
-        <v>102</v>
+        <v>391</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>103</v>
+        <v>392</v>
       </c>
       <c r="J46" s="1">
-        <v>20082</v>
+        <v>20076</v>
       </c>
     </row>
     <row r="47" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H47" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J47" s="1">
-        <v>20083</v>
+        <v>20081</v>
       </c>
     </row>
     <row r="48" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H48" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J48" s="1">
-        <v>20084</v>
+        <v>20082</v>
       </c>
     </row>
     <row r="49" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H49" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J49" s="1">
-        <v>20085</v>
+        <v>20083</v>
       </c>
     </row>
     <row r="50" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H50" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J50" s="1">
-        <v>20091</v>
+        <v>20084</v>
       </c>
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H51" s="1" t="s">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J51" s="1">
-        <v>20092</v>
+        <v>20085</v>
       </c>
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="J52" s="1">
-        <v>20093</v>
+        <v>20086</v>
       </c>
     </row>
     <row r="53" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H53" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J53" s="1">
-        <v>20094</v>
+        <v>20091</v>
       </c>
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H54" s="1" t="s">
-        <v>116</v>
+        <v>256</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J54" s="1">
-        <v>20095</v>
+        <v>20092</v>
       </c>
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H55" s="1" t="s">
-        <v>118</v>
+        <v>339</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J55" s="1">
-        <v>20101</v>
+        <v>20093</v>
       </c>
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H56" s="1" t="s">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J56" s="1">
-        <v>20102</v>
+        <v>20094</v>
       </c>
     </row>
     <row r="57" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H57" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="J57" s="1">
-        <v>20103</v>
+        <v>20095</v>
       </c>
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
-        <v>122</v>
+        <v>387</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>123</v>
+        <v>388</v>
       </c>
       <c r="J58" s="1">
-        <v>20104</v>
+        <v>20096</v>
       </c>
     </row>
     <row r="59" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H59" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J59" s="1">
-        <v>20105</v>
+        <v>20101</v>
       </c>
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H60" s="1" t="s">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="J60" s="1">
-        <v>20111</v>
+        <v>20102</v>
       </c>
     </row>
     <row r="61" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H61" s="1" t="s">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>128</v>
+        <v>311</v>
       </c>
       <c r="J61" s="1">
-        <v>20112</v>
+        <v>20103</v>
       </c>
     </row>
     <row r="62" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H62" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J62" s="1">
-        <v>20113</v>
+        <v>20104</v>
       </c>
     </row>
     <row r="63" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H63" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="J63" s="1">
-        <v>20114</v>
+        <v>20105</v>
       </c>
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
-        <v>133</v>
+        <v>385</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>134</v>
+        <v>386</v>
       </c>
       <c r="J64" s="1">
-        <v>20115</v>
+        <v>20106</v>
       </c>
     </row>
     <row r="65" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H65" s="1" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="J65" s="1">
-        <v>20121</v>
+        <v>20111</v>
       </c>
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H66" s="1" t="s">
-        <v>135</v>
+        <v>254</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="J66" s="1">
-        <v>20122</v>
+        <v>20112</v>
       </c>
     </row>
     <row r="67" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H67" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="J67" s="1">
-        <v>20123</v>
+        <v>20113</v>
       </c>
     </row>
     <row r="68" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H68" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="J68" s="1">
-        <v>20124</v>
+        <v>20114</v>
       </c>
     </row>
     <row r="69" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H69" s="1" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="J69" s="1">
-        <v>20125</v>
+        <v>20115</v>
       </c>
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>165</v>
+        <v>384</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>168</v>
+        <v>383</v>
       </c>
       <c r="J70" s="1">
-        <v>20126</v>
+        <v>20116</v>
       </c>
     </row>
     <row r="71" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H71" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="J71" s="1">
-        <v>20127</v>
+        <v>20121</v>
       </c>
     </row>
     <row r="72" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H72" s="1" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="J72" s="1">
-        <v>20131</v>
+        <v>20122</v>
       </c>
     </row>
     <row r="73" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H73" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="J73" s="1">
-        <v>20132</v>
-      </c>
-    </row>
-    <row r="74" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>20123</v>
+      </c>
+    </row>
+    <row r="74" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H74" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="J74" s="1">
-        <v>20133</v>
+        <v>20124</v>
       </c>
     </row>
     <row r="75" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H75" s="1" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J75" s="1">
-        <v>20134</v>
+        <v>20125</v>
       </c>
     </row>
     <row r="76" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H76" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="J76" s="1">
-        <v>20135</v>
+        <v>20126</v>
       </c>
     </row>
     <row r="77" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H77" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J77" s="1">
-        <v>20136</v>
+        <v>20127</v>
       </c>
     </row>
     <row r="78" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H78" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J78" s="1">
-        <v>20137</v>
+        <v>20131</v>
       </c>
     </row>
     <row r="79" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H79" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="J79" s="1">
-        <v>22001</v>
-      </c>
-    </row>
-    <row r="80" spans="8:10" x14ac:dyDescent="0.2">
+        <v>20132</v>
+      </c>
+    </row>
+    <row r="80" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H80" s="1" t="s">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J80" s="1">
-        <v>22002</v>
+        <v>20133</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H81" s="1" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="J81" s="1">
-        <v>22003</v>
+        <v>20134</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
-        <v>340</v>
+        <v>177</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>332</v>
+        <v>174</v>
       </c>
       <c r="J82" s="1">
-        <v>23001</v>
+        <v>20135</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H83" s="1" t="s">
-        <v>341</v>
+        <v>178</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>333</v>
+        <v>175</v>
       </c>
       <c r="J83" s="1">
-        <v>23002</v>
+        <v>20136</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>334</v>
+        <v>179</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>337</v>
+        <v>176</v>
       </c>
       <c r="J84" s="1">
-        <v>23003</v>
+        <v>20137</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>335</v>
+        <v>153</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>338</v>
+        <v>154</v>
       </c>
       <c r="J85" s="1">
-        <v>23004</v>
+        <v>22001</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>339</v>
+        <v>155</v>
       </c>
       <c r="J86" s="1">
-        <v>23005</v>
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H87" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J87" s="1">
+        <v>22003</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H88" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J88" s="1">
+        <v>23001</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B89" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="H89" s="1" t="s">
-        <v>191</v>
+        <v>338</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="J89" s="1">
-        <v>0</v>
+        <v>23002</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H90" s="1" t="s">
-        <v>141</v>
+        <v>415</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>142</v>
+        <v>334</v>
       </c>
       <c r="J90" s="1">
-        <v>1</v>
+        <v>23003</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H91" s="1" t="s">
-        <v>143</v>
+        <v>416</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>146</v>
+        <v>335</v>
       </c>
       <c r="J91" s="1">
-        <v>2</v>
+        <v>23004</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H92" s="1" t="s">
-        <v>144</v>
+        <v>417</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>147</v>
+        <v>336</v>
       </c>
       <c r="J92" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H93" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J93" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H94" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J94" s="1">
-        <v>21001</v>
+        <v>23005</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B95" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="H95" s="1" t="s">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="J95" s="1">
-        <v>21002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H96" s="1" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>258</v>
+        <v>142</v>
       </c>
       <c r="J96" s="1">
-        <v>21003</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H97" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J97" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B98" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="H98" s="1" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>290</v>
+        <v>147</v>
       </c>
       <c r="J98" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H99" s="1" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>289</v>
+        <v>148</v>
       </c>
       <c r="J99" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H100" s="1" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>288</v>
+        <v>150</v>
       </c>
       <c r="J100" s="1">
-        <v>3</v>
+        <v>21001</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H101" s="1" t="s">
-        <v>229</v>
+        <v>151</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>287</v>
+        <v>152</v>
       </c>
       <c r="J101" s="1">
-        <v>4</v>
+        <v>21002</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H102" s="1" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="J102" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H103" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="J103" s="1">
-        <v>6</v>
+        <v>21003</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B104" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="H104" s="1" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>284</v>
+        <v>192</v>
       </c>
       <c r="J104" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="1" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="J105" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H106" s="1" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="J106" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="J107" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H108" s="1" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="J108" s="1">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H109" s="1" t="s">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="J109" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>310</v>
+        <v>184</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="J110" s="1">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="1" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="J111" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="J112" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H113" s="1" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>375</v>
+        <v>282</v>
       </c>
       <c r="J113" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H114" s="1" t="s">
-        <v>278</v>
+        <v>185</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J114" s="1">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H115" s="1" t="s">
-        <v>309</v>
+        <v>186</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="J115" s="1">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="J116" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="1" t="s">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>377</v>
+        <v>305</v>
       </c>
       <c r="J117" s="1">
-        <v>20</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H118" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J118" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B119" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="H119" s="1" t="s">
-        <v>191</v>
+        <v>307</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="J119" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>202</v>
+        <v>372</v>
       </c>
       <c r="J120" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
       <c r="J121" s="1">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H122" s="1" t="s">
-        <v>195</v>
+        <v>309</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>198</v>
+        <v>308</v>
       </c>
       <c r="J122" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H123" s="1" t="s">
-        <v>196</v>
+        <v>312</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>199</v>
+        <v>313</v>
       </c>
       <c r="J123" s="1">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H124" s="1" t="s">
-        <v>200</v>
+        <v>373</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>201</v>
+        <v>374</v>
       </c>
       <c r="J124" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B126" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="H126" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H125" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="J125" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B127" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H127" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I126" s="1" t="s">
+      <c r="I127" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J126" s="1">
+      <c r="J127" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H127" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J127" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J128" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J129" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="J130" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H131" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J131" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B132" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="H132" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J132" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B134" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J134" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H133" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="J133" s="1">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H135" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J135" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H134" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J134" s="1">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H136" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J136" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B136" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J136" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="J137" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="J138" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H139" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J139" s="1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B140" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J140" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B141" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="H141" s="1" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="J141" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H142" s="1" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="J142" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B144" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H145" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J145" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H143" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J143" s="1">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H146" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J146" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H144" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J144" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B146" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J146" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H147" s="1" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="J147" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H148" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J148" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B149" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="H149" s="1" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="J149" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H150" s="1" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="J150" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H151" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="J151" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H152" s="1" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="J152" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B154" s="1" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>191</v>
@@ -3536,10 +3792,10 @@
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H155" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="J155" s="1">
         <v>1</v>
@@ -3547,10 +3803,10 @@
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H156" s="1" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="J156" s="1">
         <v>2</v>
@@ -3558,10 +3814,10 @@
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H157" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="J157" s="1">
         <v>3</v>
@@ -3569,10 +3825,10 @@
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H158" s="1" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="J158" s="1">
         <v>4</v>
@@ -3580,290 +3836,290 @@
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H159" s="1" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="J159" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B161" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H161" s="1" t="s">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H160" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J160" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B162" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I161" s="1" t="s">
+      <c r="I162" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J161" s="1">
+      <c r="J162" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H162" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J162" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H163" s="1" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="J163" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H164" s="1" t="s">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="J164" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H165" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J165" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H166" s="1" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="J166" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H167" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J167" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B168" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="H168" s="1" t="s">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B169" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H169" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I168" s="1" t="s">
+      <c r="I169" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J168" s="1">
+      <c r="J169" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H169" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I169" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="J169" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H170" s="1" t="s">
-        <v>297</v>
+        <v>185</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="J170" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H171" s="1" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="J171" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H172" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J172" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B173" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="H173" s="1" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>192</v>
+        <v>266</v>
       </c>
       <c r="J173" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H174" s="1" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="J174" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H175" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="I175" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="J175" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B176" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>294</v>
+      </c>
       <c r="H176" s="1" t="s">
-        <v>315</v>
+        <v>191</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="J176" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H177" s="1" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="J177" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H178" s="1" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="J178" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H179" s="1" t="s">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>354</v>
+        <v>299</v>
       </c>
       <c r="J179" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H180" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="I180" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J180" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B181" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="H181" s="1" t="s">
-        <v>327</v>
+        <v>191</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>330</v>
+        <v>192</v>
       </c>
       <c r="J181" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H182" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="J182" s="1">
-        <v>9</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H183" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J183" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B184" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="H184" s="1" t="s">
-        <v>191</v>
+        <v>315</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>192</v>
+        <v>324</v>
       </c>
       <c r="J184" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H185" s="1" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="J185" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H186" s="1" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="J186" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.2">
@@ -3871,143 +4127,516 @@
         <v>350</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J187" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H188" s="1" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="J188" s="1">
-        <v>4</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H189" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J189" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B190" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="H190" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="J190" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B192" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H192" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I190" s="1" t="s">
+      <c r="I192" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J190" s="1">
+      <c r="J192" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H191" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="I191" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J191" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H192" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="J192" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="193" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H193" s="1" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="J193" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H194" s="1" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="J194" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H195" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J195" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H196" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="J196" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B196" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="H196" s="1" t="s">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B198" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H198" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I196" s="1" t="s">
+      <c r="I198" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J196" s="1">
+      <c r="J198" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H197" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="I197" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="J197" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H198" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="I198" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="J198" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H199" s="1" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="J199" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H200" s="1" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="I200" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="J200" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H201" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="J201" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H202" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="J202" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B204" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J204" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H205" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J205" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H206" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J206" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H207" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="J200" s="1">
+      <c r="I207" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J207" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H208" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J208" s="1">
         <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B210" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J210" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H211" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="J211" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H212" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J212" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H213" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J213" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H214" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J214" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H215" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="J215" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H216" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J216" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H217" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="J217" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H218" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J218" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H219" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="J219" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="220" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H220" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="J220" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H221" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="J221" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H222" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="J222" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H223" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="J223" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H224" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="J224" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B226" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J226" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H227" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="J227" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H228" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="J228" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H229" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J229" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H230" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="J230" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H231" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="J231" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B233" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J233" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H234" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="J234" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H235" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="J235" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H236" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="J236" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EB47ED-BDF2-47E0-886D-F36D351DC835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42E23EE-510B-4E96-9EB4-2BEA016EC766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="447">
   <si>
     <t>##var</t>
   </si>
@@ -1708,6 +1708,30 @@
   </si>
   <si>
     <t>ChangeKeyReason</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>药品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心法效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartMethodEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次行动前扳机(上次行动带来的效果)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2078,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L236"/>
+  <dimension ref="A1:L240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -3501,1141 +3525,1185 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B127" s="1" t="s">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H126" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="J126" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B128" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G127" s="1" t="s">
+      <c r="G128" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="H128" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I127" s="1" t="s">
+      <c r="I128" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J127" s="1">
+      <c r="J128" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H128" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="J128" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J129" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J130" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H131" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J131" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H132" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J132" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H133" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="I133" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J133" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B134" s="1" t="s">
+      <c r="H134" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="J134" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B136" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G134" s="1" t="s">
+      <c r="G136" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="H136" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I134" s="1" t="s">
+      <c r="I136" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J134" s="1">
+      <c r="J136" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H135" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J135" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H136" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="J136" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J137" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J138" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H139" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J139" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H140" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="I140" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J140" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B140" s="1" t="s">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B142" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G140" s="1" t="s">
+      <c r="G142" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H140" s="1" t="s">
+      <c r="H142" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="I142" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J140" s="1">
+      <c r="J142" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H141" s="1" t="s">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H143" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="I143" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J141" s="1">
+      <c r="J143" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H142" s="1" t="s">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H144" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I142" s="1" t="s">
+      <c r="I144" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J142" s="1">
+      <c r="J144" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B144" s="1" t="s">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="G144" s="1" t="s">
+      <c r="G146" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="H144" s="1" t="s">
+      <c r="H146" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I144" s="1" t="s">
+      <c r="I146" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J144" s="1">
+      <c r="J146" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H145" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J145" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H146" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="J146" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H147" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H148" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J148" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H149" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="I147" s="1" t="s">
+      <c r="I149" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J147" s="1">
+      <c r="J149" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B149" s="1" t="s">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="G149" s="1" t="s">
+      <c r="G151" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="H149" s="1" t="s">
+      <c r="H151" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I149" s="1" t="s">
+      <c r="I151" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J149" s="1">
+      <c r="J151" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H150" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J150" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H151" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J151" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H152" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J152" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H153" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J153" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H154" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="I152" s="1" t="s">
+      <c r="I154" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="J152" s="1">
+      <c r="J154" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B154" s="1" t="s">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G154" s="1" t="s">
+      <c r="G156" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="H156" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I154" s="1" t="s">
+      <c r="I156" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J154" s="1">
+      <c r="J156" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H155" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="J155" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H156" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J156" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H157" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J157" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H158" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J158" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H159" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J159" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H160" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J160" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H161" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J161" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H162" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="I162" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J162" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B162" s="1" t="s">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B164" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G162" s="1" t="s">
+      <c r="G164" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H162" s="1" t="s">
+      <c r="H164" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I162" s="1" t="s">
+      <c r="I164" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J162" s="1">
+      <c r="J164" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H163" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I163" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="J163" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H164" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="J164" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H165" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J165" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H166" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J166" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H167" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J167" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H168" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J168" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H169" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="I167" s="1" t="s">
+      <c r="I169" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J167" s="1">
+      <c r="J169" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B169" s="1" t="s">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B171" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G169" s="1" t="s">
+      <c r="G171" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="H171" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I169" s="1" t="s">
+      <c r="I171" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J169" s="1">
+      <c r="J171" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H170" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I170" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J170" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H171" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="I171" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J171" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H172" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="J172" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H173" s="1" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J173" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H174" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J174" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H175" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="J175" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H176" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="I174" s="1" t="s">
+      <c r="I176" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="J174" s="1">
+      <c r="J176" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B176" s="1" t="s">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B178" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G176" s="1" t="s">
+      <c r="G178" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="H178" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I176" s="1" t="s">
+      <c r="I178" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J176" s="1">
+      <c r="J178" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H177" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I177" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="J177" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H178" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="I178" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="J178" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H179" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J179" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H180" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J180" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H181" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="I179" s="1" t="s">
+      <c r="I181" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="J179" s="1">
+      <c r="J181" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B181" s="1" t="s">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G181" s="1" t="s">
+      <c r="G183" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="H181" s="1" t="s">
+      <c r="H183" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I181" s="1" t="s">
+      <c r="I183" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J181" s="1">
+      <c r="J183" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H182" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="I182" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J182" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H183" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="I183" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="J183" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H184" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J184" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H185" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J185" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H186" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J186" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H187" s="1" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="J187" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H188" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="J188" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H189" s="1" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="J189" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H190" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J190" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H191" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J191" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H192" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="I190" s="1" t="s">
+      <c r="I192" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="J190" s="1">
+      <c r="J192" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B192" s="1" t="s">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B194" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="G192" s="1" t="s">
+      <c r="G194" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H192" s="1" t="s">
+      <c r="H194" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I192" s="1" t="s">
+      <c r="I194" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J192" s="1">
+      <c r="J194" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H193" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="I193" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="J193" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H194" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="I194" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="J194" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H195" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J195" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H196" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J196" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H197" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J197" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H198" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="I196" s="1" t="s">
+      <c r="I198" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="J196" s="1">
+      <c r="J198" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B198" s="1" t="s">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B200" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="G198" s="1" t="s">
+      <c r="G200" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="H198" s="1" t="s">
+      <c r="H200" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I198" s="1" t="s">
+      <c r="I200" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J198" s="1">
+      <c r="J200" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H199" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="I199" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="J199" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H200" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="I200" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="J200" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H201" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J201" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H202" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="J202" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H203" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="J203" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H204" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="I202" s="1" t="s">
+      <c r="I204" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="J202" s="1">
+      <c r="J204" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B204" s="1" t="s">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B206" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="G204" s="1" t="s">
+      <c r="G206" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="H204" s="1" t="s">
+      <c r="H206" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I204" s="1" t="s">
+      <c r="I206" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J204" s="1">
+      <c r="J206" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H205" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="I205" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="J205" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H206" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="J206" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H207" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J207" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H208" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J208" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H209" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J209" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H210" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="I208" s="1" t="s">
+      <c r="I210" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="J208" s="1">
+      <c r="J210" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B210" s="1" t="s">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B212" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="G210" s="1" t="s">
+      <c r="G212" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H210" s="1" t="s">
+      <c r="H212" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I210" s="1" t="s">
+      <c r="I212" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J210" s="1">
+      <c r="J212" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H211" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="I211" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="J211" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H212" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="I212" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="J212" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H213" s="1" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="J213" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H214" s="1" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="J214" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H215" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="J215" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H216" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J216" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H217" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J217" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H218" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="J218" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H219" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J219" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H220" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="J220" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H221" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="J221" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H222" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J222" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H223" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="J223" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H224" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="J224" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H225" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="J225" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H226" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="I224" s="1" t="s">
+      <c r="I226" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="J224" s="1">
+      <c r="J226" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B226" s="1" t="s">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B228" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="G226" s="1" t="s">
+      <c r="G228" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H226" s="1" t="s">
+      <c r="H228" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I226" s="1" t="s">
+      <c r="I228" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J226" s="1">
+      <c r="J228" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H227" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="I227" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="J227" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H228" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="I228" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="J228" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H229" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J229" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H230" s="1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="J230" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H231" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J231" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H232" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="J232" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H233" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="I231" s="1" t="s">
+      <c r="I233" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J231" s="1">
+      <c r="J233" s="1">
         <v>5</v>
-      </c>
-    </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B233" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="H233" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I233" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J233" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H234" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J234" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H235" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="J235" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B237" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J237" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H238" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="J238" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H239" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="I235" s="1" t="s">
+      <c r="I239" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J235" s="1">
+      <c r="J239" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H236" s="1" t="s">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H240" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="I236" s="1" t="s">
+      <c r="I240" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="J236" s="1">
+      <c r="J240" s="1">
         <v>3</v>
       </c>
     </row>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42E23EE-510B-4E96-9EB4-2BEA016EC766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB86205-815D-48D4-8FDC-0981E930C092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="451">
   <si>
     <t>##var</t>
   </si>
@@ -577,22 +577,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>伤害减免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技能伤害百分比变动</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>杀式伤害直接减免</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KillingDamageReduceInt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GangQiRecNatural</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1732,6 +1720,34 @@
   </si>
   <si>
     <t>下次行动前扳机(上次行动带来的效果)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么时候获取属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetPropertySourceType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受伤时获取属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReceiveSkillDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potion</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2102,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L240"/>
+  <dimension ref="A1:L243"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2209,10 +2225,10 @@
         <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -2605,10 +2621,10 @@
     </row>
     <row r="40" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H40" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J40" s="1">
         <v>20066</v>
@@ -2671,10 +2687,10 @@
     </row>
     <row r="46" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H46" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J46" s="1">
         <v>20076</v>
@@ -2737,10 +2753,10 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J52" s="1">
         <v>20086</v>
@@ -2759,7 +2775,7 @@
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H54" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>112</v>
@@ -2770,7 +2786,7 @@
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H55" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>113</v>
@@ -2803,10 +2819,10 @@
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J58" s="1">
         <v>20096</v>
@@ -2825,7 +2841,7 @@
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H60" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>120</v>
@@ -2839,7 +2855,7 @@
         <v>121</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J61" s="1">
         <v>20103</v>
@@ -2869,10 +2885,10 @@
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J64" s="1">
         <v>20106</v>
@@ -2891,7 +2907,7 @@
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H66" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>128</v>
@@ -2935,10 +2951,10 @@
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J70" s="1">
         <v>20116</v>
@@ -2946,10 +2962,10 @@
     </row>
     <row r="71" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H71" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J71" s="1">
         <v>20121</v>
@@ -2960,7 +2976,7 @@
         <v>135</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J72" s="1">
         <v>20122</v>
@@ -2971,7 +2987,7 @@
         <v>136</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J73" s="1">
         <v>20123</v>
@@ -2982,7 +2998,7 @@
         <v>137</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J74" s="1">
         <v>20124</v>
@@ -2990,10 +3006,10 @@
     </row>
     <row r="75" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="J75" s="1">
         <v>20125</v>
@@ -3001,10 +3017,10 @@
     </row>
     <row r="76" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H76" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="J76" s="1">
         <v>20126</v>
@@ -3012,10 +3028,10 @@
     </row>
     <row r="77" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H77" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="J77" s="1">
         <v>20127</v>
@@ -3023,10 +3039,10 @@
     </row>
     <row r="78" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H78" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J78" s="1">
         <v>20131</v>
@@ -3037,7 +3053,7 @@
         <v>138</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J79" s="1">
         <v>20132</v>
@@ -3048,7 +3064,7 @@
         <v>139</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J80" s="1">
         <v>20133</v>
@@ -3059,7 +3075,7 @@
         <v>140</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J81" s="1">
         <v>20134</v>
@@ -3067,10 +3083,10 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J82" s="1">
         <v>20135</v>
@@ -3078,10 +3094,10 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H83" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J83" s="1">
         <v>20136</v>
@@ -3089,10 +3105,10 @@
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J84" s="1">
         <v>20137</v>
@@ -3103,7 +3119,7 @@
         <v>153</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>154</v>
+        <v>448</v>
       </c>
       <c r="J85" s="1">
         <v>22001</v>
@@ -3111,10 +3127,10 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J86" s="1">
         <v>22002</v>
@@ -3122,363 +3138,363 @@
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H87" s="1" t="s">
-        <v>157</v>
+        <v>334</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>156</v>
+        <v>329</v>
       </c>
       <c r="J87" s="1">
-        <v>22003</v>
+        <v>23001</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H88" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J88" s="1">
-        <v>23001</v>
+        <v>23002</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H89" s="1" t="s">
-        <v>338</v>
+        <v>412</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J89" s="1">
-        <v>23002</v>
+        <v>23003</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H90" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J90" s="1">
-        <v>23003</v>
+        <v>23004</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H91" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J91" s="1">
-        <v>23004</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H92" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="J92" s="1">
         <v>23005</v>
       </c>
     </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J94" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B95" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="H95" s="1" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="J95" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H96" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H97" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J97" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H98" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J98" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H99" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J99" s="1">
-        <v>4</v>
+        <v>21001</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H100" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J100" s="1">
-        <v>21001</v>
+        <v>21002</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H101" s="1" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>152</v>
+        <v>255</v>
       </c>
       <c r="J101" s="1">
-        <v>21002</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H102" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="J102" s="1">
         <v>21003</v>
       </c>
     </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B103" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J103" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B104" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="H104" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="J104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J105" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H106" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J106" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="1" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J107" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H108" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J108" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H109" s="1" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J109" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J110" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J111" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="J112" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H113" s="1" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="J113" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H114" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J114" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H115" s="1" t="s">
-        <v>186</v>
+        <v>300</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="J115" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J116" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="1" t="s">
-        <v>310</v>
+        <v>184</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="J117" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H118" s="1" t="s">
-        <v>187</v>
+        <v>304</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="J118" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H119" s="1" t="s">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="J119" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>372</v>
+        <v>276</v>
       </c>
       <c r="J120" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="J121" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
@@ -3486,365 +3502,365 @@
         <v>309</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J122" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H123" s="1" t="s">
-        <v>312</v>
+        <v>370</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="J123" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H124" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I124" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="I124" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="J124" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H125" s="1" t="s">
-        <v>375</v>
+        <v>273</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>376</v>
+        <v>443</v>
       </c>
       <c r="J125" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H126" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="J126" s="1">
         <v>22</v>
       </c>
     </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B127" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J127" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B128" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G128" s="1" t="s">
+      <c r="H128" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H128" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="I128" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="J129" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J130" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H131" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J131" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H132" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J132" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H133" s="1" t="s">
-        <v>200</v>
+        <v>438</v>
       </c>
       <c r="I133" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="J133" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B135" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J133" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H134" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="J134" s="1">
-        <v>6</v>
+      <c r="G135" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J135" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B136" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="H136" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="J136" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H137" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J137" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H138" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J138" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H139" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I139" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J139" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B141" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H142" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J139" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H140" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J140" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B142" s="1" t="s">
+      <c r="I142" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G142" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="J142" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H143" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I143" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I143" s="1" t="s">
+      <c r="J143" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J143" s="1">
+      <c r="G145" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H146" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J146" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H144" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J144" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B146" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J146" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H147" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H148" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J148" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H149" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J149" s="1">
         <v>3</v>
       </c>
     </row>
+    <row r="150" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B150" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J150" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B151" s="1" t="s">
+      <c r="H151" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I151" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="G151" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="J151" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H152" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I152" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="I152" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="J152" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H153" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="J153" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B155" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="I153" s="1" t="s">
+      <c r="G155" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="J153" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H154" s="1" t="s">
+      <c r="H155" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H156" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I156" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="I154" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J154" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B156" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="J156" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H157" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J157" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
@@ -3855,223 +3871,223 @@
         <v>244</v>
       </c>
       <c r="J158" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H159" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>247</v>
       </c>
       <c r="J159" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H160" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="I160" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="J160" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H161" s="1" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="J161" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H162" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="J162" s="1">
         <v>6</v>
       </c>
     </row>
+    <row r="163" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B163" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J163" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B164" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="H164" s="1" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="J164" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H165" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J165" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H166" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J166" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H167" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J167" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H168" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I168" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J168" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B170" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J168" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H169" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="I169" s="1" t="s">
+      <c r="G170" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J169" s="1">
-        <v>5</v>
+      <c r="H170" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J170" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B171" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="H171" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="J171" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H172" s="1" t="s">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J172" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H173" s="1" t="s">
-        <v>276</v>
+        <v>183</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J173" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H174" s="1" t="s">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="J174" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H175" s="1" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="J175" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H176" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="J176" s="1">
         <v>5</v>
       </c>
     </row>
+    <row r="177" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B177" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J177" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B178" s="1" t="s">
+      <c r="H178" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="I178" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G178" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="H178" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I178" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="J178" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H179" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I179" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I179" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="J179" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.2">
@@ -4079,505 +4095,505 @@
         <v>297</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J180" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H181" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="I181" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="J181" s="1">
         <v>3</v>
       </c>
     </row>
+    <row r="182" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B182" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J182" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B183" s="1" t="s">
+      <c r="H183" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G183" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="H183" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="I183" s="1" t="s">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="J183" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H184" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J184" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H185" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J185" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H186" s="1" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="J186" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H187" s="1" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J187" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H188" s="1" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="J188" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H189" s="1" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="J189" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H190" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J190" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H191" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J191" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H192" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="J192" s="1">
         <v>9</v>
       </c>
     </row>
+    <row r="193" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B193" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J193" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B194" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="G194" s="1" t="s">
+      <c r="H194" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I194" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H194" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I194" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="J194" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H195" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J195" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H196" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J196" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H197" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J197" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H198" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="I198" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B199" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="J198" s="1">
-        <v>4</v>
+      <c r="G199" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J199" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B200" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="H200" s="1" t="s">
-        <v>191</v>
+        <v>355</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>192</v>
+        <v>351</v>
       </c>
       <c r="J200" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H201" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J201" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H202" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J202" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H203" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="J203" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B205" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G205" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="I203" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="J203" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H204" s="1" t="s">
+      <c r="H205" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J205" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H206" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I206" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="I204" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J204" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B206" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="J206" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H207" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J207" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H208" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J208" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H209" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J209" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H210" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="I210" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="J210" s="1">
         <v>4</v>
       </c>
     </row>
+    <row r="211" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B211" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J211" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B212" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="G212" s="1" t="s">
+      <c r="H212" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I212" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H212" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I212" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="J212" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H213" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="I213" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="I213" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="J213" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H214" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="J214" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H215" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J215" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H216" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J216" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H217" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J217" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H218" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J218" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H219" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>403</v>
       </c>
       <c r="J219" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H220" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I220" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="I220" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="J220" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H221" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I221" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="I221" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="J221" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H222" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I222" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="I222" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="J222" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H223" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="I223" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="I223" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="J223" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H224" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J224" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H225" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="J225" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H226" s="1" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="J226" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B228" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J228" s="1">
         <v>0</v>
@@ -4585,10 +4601,10 @@
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H229" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J229" s="1">
         <v>1</v>
@@ -4596,10 +4612,10 @@
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H230" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="J230" s="1">
         <v>2</v>
@@ -4607,10 +4623,10 @@
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H231" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J231" s="1">
         <v>3</v>
@@ -4618,10 +4634,10 @@
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H232" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J232" s="1">
         <v>4</v>
@@ -4629,10 +4645,10 @@
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H233" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="J233" s="1">
         <v>5</v>
@@ -4640,10 +4656,10 @@
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H234" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J234" s="1">
         <v>6</v>
@@ -4651,10 +4667,10 @@
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H235" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J235" s="1">
         <v>7</v>
@@ -4662,13 +4678,13 @@
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B237" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J237" s="1">
         <v>0</v>
@@ -4676,10 +4692,10 @@
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H238" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I238" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="I238" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="J238" s="1">
         <v>1</v>
@@ -4687,10 +4703,10 @@
     </row>
     <row r="239" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H239" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I239" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="I239" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="J239" s="1">
         <v>2</v>
@@ -4698,13 +4714,41 @@
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H240" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I240" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="I240" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="J240" s="1">
         <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B242" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J242" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H243" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="J243" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB86205-815D-48D4-8FDC-0981E930C092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16C49CF-867C-4DE7-B2EA-1C98FFD5DEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="465">
   <si>
     <t>##var</t>
   </si>
@@ -1748,6 +1748,62 @@
   </si>
   <si>
     <t>Potion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetSkillCostView</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取技能显示消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取技能真实消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetSkillCostLogic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetSkillCostCheck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取技能判断消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeKeyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改变键的类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Convert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2118,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L243"/>
+  <dimension ref="A1:L251"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -4751,6 +4807,89 @@
         <v>1</v>
       </c>
     </row>
+    <row r="244" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H244" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="J244" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H245" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="J245" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H246" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="J246" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B248" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J248" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H249" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J249" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H250" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J250" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H251" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J251" s="1">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16C49CF-867C-4DE7-B2EA-1C98FFD5DEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA6ACC-3C6C-4198-A260-A9E261FD0B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="467">
   <si>
     <t>##var</t>
   </si>
@@ -573,14 +573,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DamageReducePct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能伤害百分比变动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GangQiRecNatural</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -750,10 +742,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SkillDamageRateFloor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SkillType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1272,10 +1260,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>临时的招式威力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>临时的武杀式招式威力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1596,10 +1580,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TempSkillAddWellyRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TempPowerSkillAddWellyRate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1739,10 +1719,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>伤害减免百分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>药</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1804,6 +1780,38 @@
   </si>
   <si>
     <t>转化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TreasureEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝器效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TreasureFeature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝器特性标签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JinGangSan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金刚伞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DuMengZhou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渡梦舟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2174,7 +2182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L251"/>
+  <dimension ref="A1:L253"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2281,10 +2289,10 @@
         <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -2677,10 +2685,10 @@
     </row>
     <row r="40" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H40" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="J40" s="1">
         <v>20066</v>
@@ -2743,10 +2751,10 @@
     </row>
     <row r="46" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H46" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J46" s="1">
         <v>20076</v>
@@ -2809,10 +2817,10 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="J52" s="1">
         <v>20086</v>
@@ -2831,7 +2839,7 @@
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H54" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>112</v>
@@ -2842,7 +2850,7 @@
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H55" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>113</v>
@@ -2875,10 +2883,10 @@
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J58" s="1">
         <v>20096</v>
@@ -2897,7 +2905,7 @@
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H60" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>120</v>
@@ -2911,7 +2919,7 @@
         <v>121</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J61" s="1">
         <v>20103</v>
@@ -2941,10 +2949,10 @@
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J64" s="1">
         <v>20106</v>
@@ -2963,7 +2971,7 @@
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H66" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>128</v>
@@ -3007,10 +3015,10 @@
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="J70" s="1">
         <v>20116</v>
@@ -3018,10 +3026,10 @@
     </row>
     <row r="71" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H71" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="J71" s="1">
         <v>20121</v>
@@ -3032,7 +3040,7 @@
         <v>135</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J72" s="1">
         <v>20122</v>
@@ -3043,7 +3051,7 @@
         <v>136</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J73" s="1">
         <v>20123</v>
@@ -3054,7 +3062,7 @@
         <v>137</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J74" s="1">
         <v>20124</v>
@@ -3062,10 +3070,10 @@
     </row>
     <row r="75" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H75" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J75" s="1">
         <v>20125</v>
@@ -3073,10 +3081,10 @@
     </row>
     <row r="76" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H76" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J76" s="1">
         <v>20126</v>
@@ -3084,10 +3092,10 @@
     </row>
     <row r="77" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H77" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J77" s="1">
         <v>20127</v>
@@ -3095,10 +3103,10 @@
     </row>
     <row r="78" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H78" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J78" s="1">
         <v>20131</v>
@@ -3109,7 +3117,7 @@
         <v>138</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J79" s="1">
         <v>20132</v>
@@ -3120,7 +3128,7 @@
         <v>139</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J80" s="1">
         <v>20133</v>
@@ -3131,7 +3139,7 @@
         <v>140</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J81" s="1">
         <v>20134</v>
@@ -3139,10 +3147,10 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J82" s="1">
         <v>20135</v>
@@ -3150,10 +3158,10 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H83" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J83" s="1">
         <v>20136</v>
@@ -3161,10 +3169,10 @@
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H84" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J84" s="1">
         <v>20137</v>
@@ -3172,231 +3180,231 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>153</v>
+        <v>330</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>448</v>
+        <v>326</v>
       </c>
       <c r="J85" s="1">
-        <v>22001</v>
+        <v>23001</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>200</v>
+        <v>331</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>154</v>
+        <v>327</v>
       </c>
       <c r="J86" s="1">
-        <v>22002</v>
+        <v>23002</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H87" s="1" t="s">
-        <v>334</v>
+        <v>408</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J87" s="1">
-        <v>23001</v>
+        <v>23004</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H88" s="1" t="s">
-        <v>335</v>
+        <v>409</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J88" s="1">
-        <v>23002</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H89" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="J89" s="1">
-        <v>23003</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H90" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="J90" s="1">
-        <v>23004</v>
+        <v>23005</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="H91" s="1" t="s">
-        <v>414</v>
+        <v>186</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>333</v>
+        <v>187</v>
       </c>
       <c r="J91" s="1">
-        <v>23005</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H92" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J92" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H93" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J93" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B94" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="H94" s="1" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="J94" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H95" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J95" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H96" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J96" s="1">
-        <v>2</v>
+        <v>21001</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H97" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J97" s="1">
-        <v>3</v>
+        <v>21002</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H98" s="1" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="J98" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H99" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J99" s="1">
-        <v>21001</v>
+        <v>21003</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B100" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="H100" s="1" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="J100" s="1">
-        <v>21002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H101" s="1" t="s">
-        <v>254</v>
+        <v>176</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="J101" s="1">
-        <v>21003</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H102" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J102" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B103" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="H103" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>189</v>
+        <v>282</v>
       </c>
       <c r="J103" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H104" s="1" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J104" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="1" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="J105" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H106" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J106" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="J107" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.2">
@@ -3404,297 +3412,297 @@
         <v>225</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J108" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H109" s="1" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J109" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="1" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J110" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="1" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J111" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
-        <v>229</v>
+        <v>297</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="J112" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H113" s="1" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="J113" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H114" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J114" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H115" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="I115" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="J115" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="J116" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="1" t="s">
-        <v>184</v>
+        <v>272</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J117" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H118" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J118" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H119" s="1" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="J119" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>275</v>
+        <v>366</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>276</v>
+        <v>367</v>
       </c>
       <c r="J120" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>305</v>
+        <v>369</v>
       </c>
       <c r="J121" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H122" s="1" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>310</v>
+        <v>438</v>
       </c>
       <c r="J122" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H123" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="J123" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B124" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="H124" s="1" t="s">
-        <v>372</v>
+        <v>186</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>373</v>
+        <v>187</v>
       </c>
       <c r="J124" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H125" s="1" t="s">
-        <v>273</v>
+        <v>188</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>443</v>
+        <v>197</v>
       </c>
       <c r="J125" s="1">
-        <v>22</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H126" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J126" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B127" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="H127" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J127" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J128" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J129" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>192</v>
+        <v>433</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>195</v>
+        <v>435</v>
       </c>
       <c r="J130" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H131" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J131" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B132" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="H132" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="J132" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H133" s="1" t="s">
-        <v>438</v>
+        <v>200</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>440</v>
+        <v>204</v>
       </c>
       <c r="J133" s="1">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H134" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J134" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B135" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G135" s="1" t="s">
+      <c r="H135" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="H135" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="I135" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="J135" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.2">
@@ -3705,68 +3713,63 @@
         <v>207</v>
       </c>
       <c r="J136" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H137" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I137" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B138" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J137" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="G138" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="H138" s="1" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="J138" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H139" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J139" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B141" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G141" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H140" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="H141" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J141" s="1">
+      <c r="I140" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J140" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B142" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J142" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H142" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J142" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.2">
@@ -3774,127 +3777,132 @@
         <v>216</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H144" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J144" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B145" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G145" s="1" t="s">
+      <c r="H145" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="H145" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="I145" s="1" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="J145" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B147" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J147" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H146" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="J146" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H147" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="J147" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H148" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="J148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H149" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J149" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H150" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J150" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B150" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J150" s="1">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J152" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H151" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J151" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H152" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="J152" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="153" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H153" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I153" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I153" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J153" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H154" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J154" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H155" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J155" s="1">
         <v>3</v>
-      </c>
-    </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B155" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J155" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.2">
@@ -3902,82 +3910,82 @@
         <v>242</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J156" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H157" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="J157" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H158" s="1" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="J158" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H159" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J159" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B160" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="H160" s="1" t="s">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="J160" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H161" s="1" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="J161" s="1">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H162" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J162" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B163" s="1" t="s">
+      <c r="H163" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="G163" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="I163" s="1" t="s">
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="J163" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.2">
@@ -3988,906 +3996,923 @@
         <v>263</v>
       </c>
       <c r="J164" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H165" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>264</v>
       </c>
       <c r="J165" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H166" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="J166" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B167" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="H167" s="1" t="s">
-        <v>261</v>
+        <v>186</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>266</v>
+        <v>187</v>
       </c>
       <c r="J167" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H168" s="1" t="s">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J168" s="1">
-        <v>5</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H169" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J169" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B170" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="H170" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>189</v>
+        <v>271</v>
       </c>
       <c r="J170" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H171" s="1" t="s">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="J171" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H172" s="1" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="J172" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H173" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J173" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B174" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>288</v>
+      </c>
       <c r="H174" s="1" t="s">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>263</v>
+        <v>187</v>
       </c>
       <c r="J174" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H175" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="J175" s="1">
-        <v>5</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H176" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J176" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B177" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="H177" s="1" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>189</v>
+        <v>293</v>
       </c>
       <c r="J177" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B179" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J179" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H178" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="I178" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="J178" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H179" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="I179" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="J179" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H180" s="1" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="J180" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H181" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="J181" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H182" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J182" s="1">
         <v>3</v>
-      </c>
-    </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B182" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="H182" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I182" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J182" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H183" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J183" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H184" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I184" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="I184" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="J184" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H185" s="1" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="J185" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H186" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J186" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H187" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="J187" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H188" s="1" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="J188" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H189" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="I189" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="J189" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B190" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>333</v>
+      </c>
       <c r="H190" s="1" t="s">
-        <v>324</v>
+        <v>186</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>327</v>
+        <v>187</v>
       </c>
       <c r="J190" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H191" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="J191" s="1">
-        <v>9</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H192" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="J192" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B193" s="1" t="s">
+      <c r="H193" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I193" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="G193" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H193" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I193" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="J193" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H194" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J194" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H195" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="I195" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="J195" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B196" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="H196" s="1" t="s">
-        <v>344</v>
+        <v>186</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>342</v>
+        <v>187</v>
       </c>
       <c r="J196" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H197" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J197" s="1">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H198" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J198" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B199" s="1" t="s">
+      <c r="H199" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I199" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G199" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I199" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="J199" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H200" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J200" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B202" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="I200" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="J200" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H201" s="1" t="s">
+      <c r="G202" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="I201" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="J201" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H202" s="1" t="s">
-        <v>357</v>
+        <v>186</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>353</v>
+        <v>187</v>
       </c>
       <c r="J202" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H203" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="J203" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H204" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I204" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="I203" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="J203" s="1">
-        <v>4</v>
+      <c r="J204" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B205" s="1" t="s">
+      <c r="H205" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I205" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="G205" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I205" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="J205" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H206" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J206" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H207" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="I207" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="J207" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B208" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J208" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H209" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="J209" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H208" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="I208" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="J208" s="1">
+    <row r="210" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H210" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J210" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H209" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="J209" s="1">
+    <row r="211" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H211" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J211" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B211" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="H211" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I211" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J211" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H212" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="J212" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H213" s="1" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="J213" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H214" s="1" t="s">
         <v>392</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J214" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H215" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J215" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H216" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J216" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="217" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H217" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J217" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="218" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H218" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="J218" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H219" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J219" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H220" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J220" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H221" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="J221" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H222" s="1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="J222" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H223" s="1" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="J223" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H224" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="I224" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J224" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B225" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="H225" s="1" t="s">
-        <v>424</v>
+        <v>186</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>425</v>
+        <v>187</v>
       </c>
       <c r="J225" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H226" s="1" t="s">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="J226" s="1">
-        <v>16</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H227" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="J227" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B228" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="H228" s="1" t="s">
-        <v>188</v>
+        <v>415</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>189</v>
+        <v>416</v>
       </c>
       <c r="J228" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H229" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I229" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="I229" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="J229" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H230" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J230" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H231" s="1" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="J231" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H232" s="1" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="J232" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H233" s="1" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="I233" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="J233" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B235" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J235" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H236" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I236" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="J233" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H234" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="I234" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="J234" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H235" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="I235" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="J235" s="1">
-        <v>7</v>
+      <c r="J236" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B237" s="1" t="s">
+      <c r="H237" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I237" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="H237" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I237" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="J237" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H238" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="I238" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="I238" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="J238" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B240" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J240" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H241" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J241" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H239" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="I239" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="J239" s="1">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H242" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="J242" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H240" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="I240" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J240" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B242" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="H242" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I242" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J242" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H243" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J243" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H244" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="J244" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B246" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="I244" s="1" t="s">
+      <c r="G246" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="J244" s="1">
+      <c r="H246" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J246" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H247" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="J247" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H248" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="J248" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H245" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="I245" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="J245" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H246" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="I246" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="J246" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B248" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H248" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I248" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J248" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="249" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H249" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I249" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="J249" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B251" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="J249" s="1">
+      <c r="G251" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J251" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H252" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I252" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J252" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H250" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="I250" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J250" s="1">
+    <row r="253" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H253" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="J253" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H251" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="I251" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="J251" s="1">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA6ACC-3C6C-4198-A260-A9E261FD0B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BD9316-7DA8-49BB-A85A-A8438302E8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="479">
   <si>
     <t>##var</t>
   </si>
@@ -1812,6 +1812,54 @@
   </si>
   <si>
     <t>渡梦舟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleMomentViewType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扳机显示类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreDoDesition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoDesition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfActionWheelStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterClash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后（受到行动后，行动后，行动结束）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预先行动决定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动决定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每一息开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CostResource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2182,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L253"/>
+  <dimension ref="A1:L268"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2192,7 +2240,7 @@
     <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -3574,10 +3622,10 @@
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
-        <v>184</v>
+        <v>467</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>185</v>
+        <v>468</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>186</v>
@@ -3591,10 +3639,10 @@
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H125" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="J125" s="1">
         <v>1</v>
@@ -3602,10 +3650,10 @@
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H126" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>192</v>
+        <v>283</v>
       </c>
       <c r="J126" s="1">
         <v>2</v>
@@ -3613,10 +3661,10 @@
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
-        <v>190</v>
+        <v>469</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>193</v>
+        <v>474</v>
       </c>
       <c r="J127" s="1">
         <v>3</v>
@@ -3624,10 +3672,10 @@
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>191</v>
+        <v>470</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>194</v>
+        <v>475</v>
       </c>
       <c r="J128" s="1">
         <v>4</v>
@@ -3635,10 +3683,10 @@
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>195</v>
+        <v>366</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>196</v>
+        <v>476</v>
       </c>
       <c r="J129" s="1">
         <v>5</v>
@@ -3646,171 +3694,181 @@
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>435</v>
+        <v>365</v>
       </c>
       <c r="J130" s="1">
         <v>6</v>
       </c>
     </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H131" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J131" s="1">
+        <v>7</v>
+      </c>
+    </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B132" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="H132" s="1" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>187</v>
+        <v>280</v>
       </c>
       <c r="J132" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H133" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>204</v>
+        <v>279</v>
       </c>
       <c r="J133" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H134" s="1" t="s">
-        <v>201</v>
+        <v>472</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="J134" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H135" s="1" t="s">
-        <v>202</v>
+        <v>477</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>206</v>
+        <v>478</v>
       </c>
       <c r="J135" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H136" s="1" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="J136" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B138" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="H138" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H137" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J137" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B139" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H139" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="I139" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J139" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H139" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="J139" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H140" s="1" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J140" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H141" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J141" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B142" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="H142" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J142" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H143" s="1" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="J143" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H144" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="J144" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H145" s="1" t="s">
-        <v>218</v>
+        <v>433</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>221</v>
+        <v>435</v>
       </c>
       <c r="J145" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B147" s="1" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>186</v>
@@ -3824,10 +3882,10 @@
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H148" s="1" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
@@ -3835,10 +3893,10 @@
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H149" s="1" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="J149" s="1">
         <v>2</v>
@@ -3846,176 +3904,171 @@
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H150" s="1" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="J150" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B152" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="H152" s="1" t="s">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H151" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J151" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B153" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I152" s="1" t="s">
+      <c r="I153" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J152" s="1">
+      <c r="J153" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H153" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J153" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H154" s="1" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="J154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H155" s="1" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="J155" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H156" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J156" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B157" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="H157" s="1" t="s">
-        <v>243</v>
+        <v>186</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="J157" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H158" s="1" t="s">
-        <v>285</v>
+        <v>216</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>286</v>
+        <v>219</v>
       </c>
       <c r="J158" s="1">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H159" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J159" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B160" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="H160" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J160" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B162" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="I162" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J162" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H161" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J161" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H162" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="J162" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H163" s="1" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="J163" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H164" s="1" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="J164" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H165" s="1" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="J165" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B167" s="1" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>186</v>
@@ -4029,10 +4082,10 @@
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H168" s="1" t="s">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="J168" s="1">
         <v>1</v>
@@ -4040,10 +4093,10 @@
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H169" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="J169" s="1">
         <v>2</v>
@@ -4051,10 +4104,10 @@
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H170" s="1" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="J170" s="1">
         <v>3</v>
@@ -4062,10 +4115,10 @@
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H171" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="J171" s="1">
         <v>4</v>
@@ -4073,704 +4126,707 @@
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H172" s="1" t="s">
-        <v>295</v>
+        <v>243</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="J172" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B174" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="H174" s="1" t="s">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H173" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J173" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B175" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H175" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I174" s="1" t="s">
+      <c r="I175" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J174" s="1">
+      <c r="J175" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H175" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="I175" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="J175" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H176" s="1" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="J176" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H177" s="1" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="J177" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H178" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J178" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B179" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="H179" s="1" t="s">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="J179" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H180" s="1" t="s">
-        <v>313</v>
+        <v>259</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="J180" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H181" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I181" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="J181" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B182" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="H182" s="1" t="s">
-        <v>309</v>
+        <v>186</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>318</v>
+        <v>187</v>
       </c>
       <c r="J182" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H183" s="1" t="s">
-        <v>319</v>
+        <v>180</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="J183" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H184" s="1" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="J184" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H185" s="1" t="s">
-        <v>343</v>
+        <v>181</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="J185" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H186" s="1" t="s">
-        <v>320</v>
+        <v>255</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>323</v>
+        <v>260</v>
       </c>
       <c r="J186" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H187" s="1" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="J187" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H188" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="I188" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="J188" s="1">
-        <v>9</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B189" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J189" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B190" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="H190" s="1" t="s">
-        <v>186</v>
+        <v>289</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>187</v>
+        <v>290</v>
       </c>
       <c r="J190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H191" s="1" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="J191" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H192" s="1" t="s">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="J192" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B194" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J194" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H195" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J195" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H196" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="J196" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H193" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="I193" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="J193" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H194" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="I194" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="J194" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B196" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I196" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J196" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H197" s="1" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="J197" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H198" s="1" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="J198" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H199" s="1" t="s">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="J199" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H200" s="1" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="J200" s="1">
-        <v>4</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H201" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J201" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B202" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="H202" s="1" t="s">
-        <v>186</v>
+        <v>321</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>187</v>
+        <v>324</v>
       </c>
       <c r="J202" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H203" s="1" t="s">
-        <v>361</v>
+        <v>322</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="J203" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H204" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="I204" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="J204" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B205" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>333</v>
+      </c>
       <c r="H205" s="1" t="s">
-        <v>363</v>
+        <v>186</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>359</v>
+        <v>187</v>
       </c>
       <c r="J205" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H206" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J206" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H207" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="J207" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H208" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="J208" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H209" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="J209" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B211" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J211" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H212" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J212" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H213" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J213" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H214" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="J214" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H215" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J215" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B217" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J217" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H218" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="J218" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H219" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="J219" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H220" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J220" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H221" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="I206" s="1" t="s">
+      <c r="I221" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="J206" s="1">
+      <c r="J221" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B208" s="1" t="s">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B223" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G208" s="1" t="s">
+      <c r="G223" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H208" s="1" t="s">
+      <c r="H223" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I208" s="1" t="s">
+      <c r="I223" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J208" s="1">
+      <c r="J223" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H209" s="1" t="s">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H224" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I209" s="1" t="s">
+      <c r="I224" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="J209" s="1">
+      <c r="J224" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H210" s="1" t="s">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H225" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I210" s="1" t="s">
+      <c r="I225" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="J210" s="1">
+      <c r="J225" s="1">
         <v>3</v>
-      </c>
-    </row>
-    <row r="211" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H211" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="I211" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="J211" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H212" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="I212" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="J212" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="213" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H213" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="I213" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="J213" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="214" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H214" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="I214" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="J214" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="215" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H215" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="I215" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="J215" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="216" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H216" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="I216" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="J216" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="217" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H217" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I217" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="J217" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="218" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H218" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="I218" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="J218" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="219" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H219" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="I219" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="J219" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="220" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H220" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I220" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="J220" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="221" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H221" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="I221" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="J221" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="222" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H222" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="I222" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="J222" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="223" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H223" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="I223" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="J223" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B225" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="H225" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I225" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J225" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H226" s="1" t="s">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="J226" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H227" s="1" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="J227" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H228" s="1" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="J228" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H229" s="1" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
       <c r="J229" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H230" s="1" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>424</v>
+        <v>396</v>
       </c>
       <c r="J230" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H231" s="1" t="s">
-        <v>433</v>
+        <v>398</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>434</v>
+        <v>399</v>
       </c>
       <c r="J231" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H232" s="1" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>436</v>
+        <v>401</v>
       </c>
       <c r="J232" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H233" s="1" t="s">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="J233" s="1">
-        <v>8</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H234" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J234" s="1">
+        <v>12</v>
       </c>
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B235" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="H235" s="1" t="s">
-        <v>186</v>
+        <v>406</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>187</v>
+        <v>407</v>
       </c>
       <c r="J235" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="236" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H236" s="1" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="J236" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H237" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="J237" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H238" s="1" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="J238" s="1">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B240" s="1" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>186</v>
@@ -4784,10 +4840,10 @@
     </row>
     <row r="241" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H241" s="1" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="J241" s="1">
         <v>1</v>
@@ -4795,10 +4851,10 @@
     </row>
     <row r="242" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H242" s="1" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="J242" s="1">
         <v>2</v>
@@ -4806,10 +4862,10 @@
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H243" s="1" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
       <c r="J243" s="1">
         <v>3</v>
@@ -4817,101 +4873,253 @@
     </row>
     <row r="244" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H244" s="1" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="J244" s="1">
         <v>4</v>
       </c>
     </row>
+    <row r="245" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H245" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J245" s="1">
+        <v>5</v>
+      </c>
+    </row>
     <row r="246" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B246" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="G246" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="H246" s="1" t="s">
-        <v>186</v>
+        <v>433</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>187</v>
+        <v>434</v>
       </c>
       <c r="J246" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H247" s="1" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="J247" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H248" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J248" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H249" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="I249" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="J249" s="1">
-        <v>3</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B250" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J250" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B251" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="H251" s="1" t="s">
-        <v>186</v>
+        <v>426</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>187</v>
+        <v>429</v>
       </c>
       <c r="J251" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H252" s="1" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="J252" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H253" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="J253" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B255" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I255" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J255" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H256" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="I256" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J256" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H257" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="J257" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H258" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I258" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="J258" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H259" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I259" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="J259" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B261" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H261" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I261" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J261" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H262" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="I262" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="J262" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H263" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I263" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="J263" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H264" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="I264" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="J264" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B266" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H266" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I266" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J266" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H267" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I267" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J267" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H268" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="I253" s="1" t="s">
+      <c r="I268" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="J253" s="1">
+      <c r="J268" s="1">
         <v>2</v>
       </c>
     </row>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BD9316-7DA8-49BB-A85A-A8438302E8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894751D0-FF3F-42C2-9E64-0370E82143FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="496">
   <si>
     <t>##var</t>
   </si>
@@ -1860,6 +1860,74 @@
   </si>
   <si>
     <t>资源消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XiaoYu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XiaoYuDengYu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DengYu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DaYuDengYu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DaYu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小于等于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大于等于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataRelation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2230,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L268"/>
+  <dimension ref="A1:L279"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -5123,6 +5191,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="270" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B270" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H270" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J270" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H271" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="I271" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="J271" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H272" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="I272" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J272" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B274" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="H274" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I274" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J274" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H275" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="I275" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="J275" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H276" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I276" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="J276" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H277" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="I277" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J277" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H278" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I278" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="J278" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H279" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="I279" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J279" s="1">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894751D0-FF3F-42C2-9E64-0370E82143FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE6A24A-A5AB-403F-995C-324E07DD498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="495">
   <si>
     <t>##var</t>
   </si>
@@ -1005,10 +1005,6 @@
   </si>
   <si>
     <t>技能释放成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelStart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2801,10 +2797,10 @@
     </row>
     <row r="40" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H40" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="J40" s="1">
         <v>20066</v>
@@ -2867,10 +2863,10 @@
     </row>
     <row r="46" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H46" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="J46" s="1">
         <v>20076</v>
@@ -2933,10 +2929,10 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J52" s="1">
         <v>20086</v>
@@ -2966,7 +2962,7 @@
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H55" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>113</v>
@@ -2999,10 +2995,10 @@
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="J58" s="1">
         <v>20096</v>
@@ -3035,7 +3031,7 @@
         <v>121</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J61" s="1">
         <v>20103</v>
@@ -3065,10 +3061,10 @@
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="J64" s="1">
         <v>20106</v>
@@ -3131,10 +3127,10 @@
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J70" s="1">
         <v>20116</v>
@@ -3296,10 +3292,10 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J85" s="1">
         <v>23001</v>
@@ -3307,10 +3303,10 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J86" s="1">
         <v>23002</v>
@@ -3318,10 +3314,10 @@
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H87" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J87" s="1">
         <v>23004</v>
@@ -3329,10 +3325,10 @@
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H88" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J88" s="1">
         <v>23005</v>
@@ -3451,7 +3447,7 @@
         <v>176</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J101" s="1">
         <v>1</v>
@@ -3462,7 +3458,7 @@
         <v>177</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J102" s="1">
         <v>2</v>
@@ -3473,7 +3469,7 @@
         <v>178</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J103" s="1">
         <v>3</v>
@@ -3484,7 +3480,7 @@
         <v>223</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J104" s="1">
         <v>4</v>
@@ -3495,7 +3491,7 @@
         <v>222</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
@@ -3506,7 +3502,7 @@
         <v>179</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J106" s="1">
         <v>6</v>
@@ -3517,7 +3513,7 @@
         <v>224</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J107" s="1">
         <v>7</v>
@@ -3528,7 +3524,7 @@
         <v>225</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J108" s="1">
         <v>8</v>
@@ -3539,7 +3535,7 @@
         <v>226</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J109" s="1">
         <v>9</v>
@@ -3550,7 +3546,7 @@
         <v>180</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J110" s="1">
         <v>10</v>
@@ -3561,7 +3557,7 @@
         <v>181</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J111" s="1">
         <v>11</v>
@@ -3569,10 +3565,10 @@
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I112" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="J112" s="1">
         <v>12</v>
@@ -3580,10 +3576,10 @@
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H113" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J113" s="1">
         <v>13</v>
@@ -3594,7 +3590,7 @@
         <v>182</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J114" s="1">
         <v>14</v>
@@ -3602,10 +3598,10 @@
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H115" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J115" s="1">
         <v>15</v>
@@ -3613,10 +3609,10 @@
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
-        <v>265</v>
+        <v>470</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J116" s="1">
         <v>16</v>
@@ -3624,10 +3620,10 @@
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I117" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="J117" s="1">
         <v>17</v>
@@ -3635,10 +3631,10 @@
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H118" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J118" s="1">
         <v>18</v>
@@ -3646,10 +3642,10 @@
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H119" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I119" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="J119" s="1">
         <v>19</v>
@@ -3657,10 +3653,10 @@
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I120" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="J120" s="1">
         <v>20</v>
@@ -3668,10 +3664,10 @@
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I121" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="J121" s="1">
         <v>21</v>
@@ -3679,10 +3675,10 @@
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H122" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J122" s="1">
         <v>22</v>
@@ -3690,10 +3686,10 @@
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>186</v>
@@ -3710,7 +3706,7 @@
         <v>176</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J125" s="1">
         <v>1</v>
@@ -3721,7 +3717,7 @@
         <v>177</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J126" s="1">
         <v>2</v>
@@ -3729,10 +3725,10 @@
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J127" s="1">
         <v>3</v>
@@ -3740,10 +3736,10 @@
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J128" s="1">
         <v>4</v>
@@ -3751,10 +3747,10 @@
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J129" s="1">
         <v>5</v>
@@ -3762,10 +3758,10 @@
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J130" s="1">
         <v>6</v>
@@ -3776,7 +3772,7 @@
         <v>223</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J131" s="1">
         <v>7</v>
@@ -3787,7 +3783,7 @@
         <v>222</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J132" s="1">
         <v>8</v>
@@ -3798,7 +3794,7 @@
         <v>179</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J133" s="1">
         <v>9</v>
@@ -3806,10 +3802,10 @@
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H134" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J134" s="1">
         <v>10</v>
@@ -3817,10 +3813,10 @@
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H135" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I135" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="J135" s="1">
         <v>11</v>
@@ -3831,7 +3827,7 @@
         <v>226</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J136" s="1">
         <v>12</v>
@@ -3842,7 +3838,7 @@
         <v>180</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J137" s="1">
         <v>13</v>
@@ -3922,10 +3918,10 @@
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H145" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J145" s="1">
         <v>6</v>
@@ -4205,10 +4201,10 @@
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H173" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I173" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="J173" s="1">
         <v>6</v>
@@ -4288,10 +4284,10 @@
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B182" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G182" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>186</v>
@@ -4308,7 +4304,7 @@
         <v>180</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J183" s="1">
         <v>1</v>
@@ -4316,10 +4312,10 @@
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H184" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J184" s="1">
         <v>2</v>
@@ -4330,7 +4326,7 @@
         <v>181</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J185" s="1">
         <v>3</v>
@@ -4349,10 +4345,10 @@
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H187" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I187" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="I187" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="J187" s="1">
         <v>5</v>
@@ -4360,10 +4356,10 @@
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B189" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G189" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>186</v>
@@ -4377,10 +4373,10 @@
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H190" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I190" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="I190" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="J190" s="1">
         <v>1</v>
@@ -4388,10 +4384,10 @@
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H191" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I191" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="I191" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="J191" s="1">
         <v>2</v>
@@ -4399,10 +4395,10 @@
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H192" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J192" s="1">
         <v>3</v>
@@ -4410,10 +4406,10 @@
     </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B194" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>186</v>
@@ -4427,10 +4423,10 @@
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H195" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J195" s="1">
         <v>1</v>
@@ -4438,10 +4434,10 @@
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H196" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J196" s="1">
         <v>2</v>
@@ -4449,10 +4445,10 @@
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H197" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J197" s="1">
         <v>3</v>
@@ -4460,10 +4456,10 @@
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H198" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J198" s="1">
         <v>4</v>
@@ -4471,10 +4467,10 @@
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H199" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J199" s="1">
         <v>5</v>
@@ -4482,10 +4478,10 @@
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H200" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I200" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="I200" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="J200" s="1">
         <v>6</v>
@@ -4493,10 +4489,10 @@
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H201" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J201" s="1">
         <v>7</v>
@@ -4504,10 +4500,10 @@
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H202" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J202" s="1">
         <v>8</v>
@@ -4515,10 +4511,10 @@
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H203" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J203" s="1">
         <v>9</v>
@@ -4526,10 +4522,10 @@
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B205" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H205" s="1" t="s">
         <v>186</v>
@@ -4543,10 +4539,10 @@
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H206" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I206" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="J206" s="1">
         <v>1</v>
@@ -4554,10 +4550,10 @@
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H207" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J207" s="1">
         <v>2</v>
@@ -4565,10 +4561,10 @@
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H208" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J208" s="1">
         <v>3</v>
@@ -4576,10 +4572,10 @@
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H209" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I209" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="J209" s="1">
         <v>4</v>
@@ -4587,10 +4583,10 @@
     </row>
     <row r="211" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B211" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G211" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>186</v>
@@ -4604,10 +4600,10 @@
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H212" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J212" s="1">
         <v>1</v>
@@ -4615,10 +4611,10 @@
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H213" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J213" s="1">
         <v>2</v>
@@ -4626,10 +4622,10 @@
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H214" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J214" s="1">
         <v>3</v>
@@ -4637,10 +4633,10 @@
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H215" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J215" s="1">
         <v>4</v>
@@ -4648,10 +4644,10 @@
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B217" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G217" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>186</v>
@@ -4665,10 +4661,10 @@
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H218" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J218" s="1">
         <v>1</v>
@@ -4676,10 +4672,10 @@
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H219" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J219" s="1">
         <v>2</v>
@@ -4687,10 +4683,10 @@
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H220" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J220" s="1">
         <v>3</v>
@@ -4698,10 +4694,10 @@
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H221" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J221" s="1">
         <v>4</v>
@@ -4709,10 +4705,10 @@
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B223" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>186</v>
@@ -4726,10 +4722,10 @@
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H224" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I224" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="I224" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="J224" s="1">
         <v>2</v>
@@ -4737,10 +4733,10 @@
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H225" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="I225" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="I225" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="J225" s="1">
         <v>3</v>
@@ -4748,10 +4744,10 @@
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H226" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="I226" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="I226" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="J226" s="1">
         <v>4</v>
@@ -4759,10 +4755,10 @@
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H227" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J227" s="1">
         <v>5</v>
@@ -4770,10 +4766,10 @@
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H228" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J228" s="1">
         <v>6</v>
@@ -4781,10 +4777,10 @@
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H229" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J229" s="1">
         <v>7</v>
@@ -4792,10 +4788,10 @@
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H230" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J230" s="1">
         <v>8</v>
@@ -4803,10 +4799,10 @@
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H231" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I231" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="I231" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="J231" s="1">
         <v>9</v>
@@ -4814,10 +4810,10 @@
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H232" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="I232" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="I232" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="J232" s="1">
         <v>10</v>
@@ -4825,10 +4821,10 @@
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H233" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I233" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="I233" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="J233" s="1">
         <v>11</v>
@@ -4836,10 +4832,10 @@
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H234" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I234" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="I234" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="J234" s="1">
         <v>12</v>
@@ -4847,10 +4843,10 @@
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H235" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I235" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="I235" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="J235" s="1">
         <v>13</v>
@@ -4858,10 +4854,10 @@
     </row>
     <row r="236" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H236" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J236" s="1">
         <v>14</v>
@@ -4869,10 +4865,10 @@
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H237" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I237" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="I237" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="J237" s="1">
         <v>15</v>
@@ -4880,10 +4876,10 @@
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H238" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J238" s="1">
         <v>16</v>
@@ -4891,10 +4887,10 @@
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B240" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>186</v>
@@ -4908,10 +4904,10 @@
     </row>
     <row r="241" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H241" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="I241" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="I241" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="J241" s="1">
         <v>1</v>
@@ -4919,10 +4915,10 @@
     </row>
     <row r="242" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H242" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I242" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="I242" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="J242" s="1">
         <v>2</v>
@@ -4930,10 +4926,10 @@
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H243" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I243" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="I243" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="J243" s="1">
         <v>3</v>
@@ -4941,10 +4937,10 @@
     </row>
     <row r="244" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H244" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I244" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="I244" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="J244" s="1">
         <v>4</v>
@@ -4952,10 +4948,10 @@
     </row>
     <row r="245" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H245" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I245" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="I245" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="J245" s="1">
         <v>5</v>
@@ -4963,10 +4959,10 @@
     </row>
     <row r="246" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H246" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I246" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="I246" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="J246" s="1">
         <v>6</v>
@@ -4974,10 +4970,10 @@
     </row>
     <row r="247" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H247" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J247" s="1">
         <v>7</v>
@@ -4985,10 +4981,10 @@
     </row>
     <row r="248" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H248" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="I248" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="I248" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="J248" s="1">
         <v>8</v>
@@ -4996,7 +4992,7 @@
     </row>
     <row r="250" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B250" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H250" s="1" t="s">
         <v>186</v>
@@ -5010,10 +5006,10 @@
     </row>
     <row r="251" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H251" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J251" s="1">
         <v>1</v>
@@ -5021,10 +5017,10 @@
     </row>
     <row r="252" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H252" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J252" s="1">
         <v>2</v>
@@ -5032,10 +5028,10 @@
     </row>
     <row r="253" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H253" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J253" s="1">
         <v>3</v>
@@ -5043,10 +5039,10 @@
     </row>
     <row r="255" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B255" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>186</v>
@@ -5060,10 +5056,10 @@
     </row>
     <row r="256" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H256" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J256" s="1">
         <v>1</v>
@@ -5071,10 +5067,10 @@
     </row>
     <row r="257" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H257" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I257" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="I257" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="J257" s="1">
         <v>2</v>
@@ -5082,10 +5078,10 @@
     </row>
     <row r="258" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H258" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I258" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="I258" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="J258" s="1">
         <v>3</v>
@@ -5093,10 +5089,10 @@
     </row>
     <row r="259" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H259" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J259" s="1">
         <v>4</v>
@@ -5104,10 +5100,10 @@
     </row>
     <row r="261" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B261" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G261" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="H261" s="1" t="s">
         <v>186</v>
@@ -5121,10 +5117,10 @@
     </row>
     <row r="262" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H262" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J262" s="1">
         <v>1</v>
@@ -5132,10 +5128,10 @@
     </row>
     <row r="263" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H263" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J263" s="1">
         <v>2</v>
@@ -5143,10 +5139,10 @@
     </row>
     <row r="264" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H264" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="I264" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="I264" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="J264" s="1">
         <v>3</v>
@@ -5154,10 +5150,10 @@
     </row>
     <row r="266" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B266" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G266" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="H266" s="1" t="s">
         <v>186</v>
@@ -5171,10 +5167,10 @@
     </row>
     <row r="267" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H267" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="I267" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="I267" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="J267" s="1">
         <v>1</v>
@@ -5182,10 +5178,10 @@
     </row>
     <row r="268" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H268" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="I268" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="I268" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="J268" s="1">
         <v>2</v>
@@ -5193,10 +5189,10 @@
     </row>
     <row r="270" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B270" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>186</v>
@@ -5210,10 +5206,10 @@
     </row>
     <row r="271" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H271" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J271" s="1">
         <v>1</v>
@@ -5221,10 +5217,10 @@
     </row>
     <row r="272" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H272" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J272" s="1">
         <v>2</v>
@@ -5232,7 +5228,7 @@
     </row>
     <row r="274" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B274" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>186</v>
@@ -5246,10 +5242,10 @@
     </row>
     <row r="275" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H275" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J275" s="1">
         <v>1</v>
@@ -5257,10 +5253,10 @@
     </row>
     <row r="276" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H276" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J276" s="1">
         <v>2</v>
@@ -5268,10 +5264,10 @@
     </row>
     <row r="277" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H277" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J277" s="1">
         <v>3</v>
@@ -5279,10 +5275,10 @@
     </row>
     <row r="278" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H278" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J278" s="1">
         <v>4</v>
@@ -5290,10 +5286,10 @@
     </row>
     <row r="279" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H279" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J279" s="1">
         <v>5</v>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE6A24A-A5AB-403F-995C-324E07DD498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901194DE-BB6A-4131-996F-E60C62CD0A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1188,10 +1188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DamageBase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CheckCost</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1200,14 +1196,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>技能预先伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能基础伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技能预先消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1220,10 +1208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DamagePreview</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KeyPreview</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1316,14 +1300,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DamageCurr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能当前伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>WeatherType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1576,14 +1552,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TempPowerSkillAddWellyRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TempArtSkillAddWellyRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>无法直接清除异常状态</t>
   </si>
   <si>
@@ -1924,6 +1892,38 @@
   </si>
   <si>
     <t>DataRelation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WellyRatePreview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WellyRateBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WellyRateCurr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能预先威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能基础威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能当前威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempPowerSkillWellyRateEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TempArtSkillWellyRateEx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="40" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H40" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="J40" s="1">
         <v>20066</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="46" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H46" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="J46" s="1">
         <v>20076</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J52" s="1">
         <v>20086</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H55" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>113</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="J58" s="1">
         <v>20096</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J64" s="1">
         <v>20106</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="J70" s="1">
         <v>20116</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J85" s="1">
         <v>23001</v>
@@ -3303,10 +3303,10 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H86" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J86" s="1">
         <v>23002</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H87" s="1" t="s">
-        <v>407</v>
+        <v>493</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J87" s="1">
         <v>23004</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H88" s="1" t="s">
-        <v>408</v>
+        <v>494</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J88" s="1">
         <v>23005</v>
@@ -3609,10 +3609,10 @@
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="J116" s="1">
         <v>16</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="J120" s="1">
         <v>20</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="J121" s="1">
         <v>21</v>
@@ -3678,7 +3678,7 @@
         <v>269</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="J122" s="1">
         <v>22</v>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>186</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="J127" s="1">
         <v>3</v>
@@ -3736,10 +3736,10 @@
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="J128" s="1">
         <v>4</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="J129" s="1">
         <v>5</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="J130" s="1">
         <v>6</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H134" s="1" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>277</v>
@@ -3813,10 +3813,10 @@
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H135" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="J135" s="1">
         <v>11</v>
@@ -3838,7 +3838,7 @@
         <v>180</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="J137" s="1">
         <v>13</v>
@@ -3918,10 +3918,10 @@
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H145" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="J145" s="1">
         <v>6</v>
@@ -4423,10 +4423,10 @@
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H195" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I195" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="I195" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="J195" s="1">
         <v>1</v>
@@ -4434,10 +4434,10 @@
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H196" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J196" s="1">
         <v>2</v>
@@ -4448,7 +4448,7 @@
         <v>308</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J197" s="1">
         <v>3</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H198" s="1" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>313</v>
+        <v>490</v>
       </c>
       <c r="J198" s="1">
         <v>4</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H199" s="1" t="s">
-        <v>310</v>
+        <v>488</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>314</v>
+        <v>491</v>
       </c>
       <c r="J199" s="1">
         <v>5</v>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H200" s="1" t="s">
-        <v>342</v>
+        <v>489</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>343</v>
+        <v>492</v>
       </c>
       <c r="J200" s="1">
         <v>6</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H201" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J201" s="1">
         <v>7</v>
@@ -4500,10 +4500,10 @@
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H202" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J202" s="1">
         <v>8</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H203" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J203" s="1">
         <v>9</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B205" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H205" s="1" t="s">
         <v>186</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H206" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J206" s="1">
         <v>1</v>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H207" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="J207" s="1">
         <v>2</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H208" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J208" s="1">
         <v>3</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H209" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="J209" s="1">
         <v>4</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="211" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B211" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>186</v>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H212" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="J212" s="1">
         <v>1</v>
@@ -4611,10 +4611,10 @@
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H213" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="J213" s="1">
         <v>2</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H214" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J214" s="1">
         <v>3</v>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H215" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="J215" s="1">
         <v>4</v>
@@ -4644,10 +4644,10 @@
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B217" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>186</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H218" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="J218" s="1">
         <v>1</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H219" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="J219" s="1">
         <v>2</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H220" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="J220" s="1">
         <v>3</v>
@@ -4694,10 +4694,10 @@
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H221" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="J221" s="1">
         <v>4</v>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B223" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>186</v>
@@ -4722,10 +4722,10 @@
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H224" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="J224" s="1">
         <v>2</v>
@@ -4733,10 +4733,10 @@
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H225" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="J225" s="1">
         <v>3</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H226" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="J226" s="1">
         <v>4</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H227" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="J227" s="1">
         <v>5</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H228" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="J228" s="1">
         <v>6</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H229" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="J229" s="1">
         <v>7</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H230" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="J230" s="1">
         <v>8</v>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H231" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="J231" s="1">
         <v>9</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H232" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="J232" s="1">
         <v>10</v>
@@ -4821,10 +4821,10 @@
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H233" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="J233" s="1">
         <v>11</v>
@@ -4832,10 +4832,10 @@
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H234" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="J234" s="1">
         <v>12</v>
@@ -4843,10 +4843,10 @@
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H235" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J235" s="1">
         <v>13</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="236" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H236" s="1" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="J236" s="1">
         <v>14</v>
@@ -4865,10 +4865,10 @@
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H237" s="1" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="J237" s="1">
         <v>15</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H238" s="1" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="J238" s="1">
         <v>16</v>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B240" s="1" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>186</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="241" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H241" s="1" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="J241" s="1">
         <v>1</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="242" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H242" s="1" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="J242" s="1">
         <v>2</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H243" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="J243" s="1">
         <v>3</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="244" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H244" s="1" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="J244" s="1">
         <v>4</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="245" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H245" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="J245" s="1">
         <v>5</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="246" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H246" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="J246" s="1">
         <v>6</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="247" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H247" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="J247" s="1">
         <v>7</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="248" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H248" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="J248" s="1">
         <v>8</v>
@@ -4992,7 +4992,7 @@
     </row>
     <row r="250" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B250" s="1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="H250" s="1" t="s">
         <v>186</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="251" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H251" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="J251" s="1">
         <v>1</v>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="252" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H252" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="J252" s="1">
         <v>2</v>
@@ -5028,10 +5028,10 @@
     </row>
     <row r="253" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H253" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="J253" s="1">
         <v>3</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="255" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B255" s="1" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>186</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="256" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H256" s="1" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="J256" s="1">
         <v>1</v>
@@ -5067,10 +5067,10 @@
     </row>
     <row r="257" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H257" s="1" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="J257" s="1">
         <v>2</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="258" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H258" s="1" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="J258" s="1">
         <v>3</v>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="259" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H259" s="1" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="J259" s="1">
         <v>4</v>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="261" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B261" s="1" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="H261" s="1" t="s">
         <v>186</v>
@@ -5117,10 +5117,10 @@
     </row>
     <row r="262" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H262" s="1" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="J262" s="1">
         <v>1</v>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="263" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H263" s="1" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="J263" s="1">
         <v>2</v>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="264" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H264" s="1" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="J264" s="1">
         <v>3</v>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="266" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B266" s="1" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="H266" s="1" t="s">
         <v>186</v>
@@ -5167,10 +5167,10 @@
     </row>
     <row r="267" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H267" s="1" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="J267" s="1">
         <v>1</v>
@@ -5178,10 +5178,10 @@
     </row>
     <row r="268" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H268" s="1" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="J268" s="1">
         <v>2</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="270" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B270" s="1" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>186</v>
@@ -5206,10 +5206,10 @@
     </row>
     <row r="271" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H271" s="1" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J271" s="1">
         <v>1</v>
@@ -5217,10 +5217,10 @@
     </row>
     <row r="272" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H272" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="J272" s="1">
         <v>2</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="274" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B274" s="1" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>186</v>
@@ -5242,10 +5242,10 @@
     </row>
     <row r="275" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H275" s="1" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="J275" s="1">
         <v>1</v>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="276" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H276" s="1" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="J276" s="1">
         <v>2</v>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="277" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H277" s="1" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="J277" s="1">
         <v>3</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="278" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H278" s="1" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J278" s="1">
         <v>4</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="279" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H279" s="1" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="J279" s="1">
         <v>5</v>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901194DE-BB6A-4131-996F-E60C62CD0A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6F50E1-996C-430F-AC8D-25CC76571CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="497">
   <si>
     <t>##var</t>
   </si>
@@ -1924,6 +1924,14 @@
   </si>
   <si>
     <t>TempArtSkillWellyRateEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返还</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2294,7 +2302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L279"/>
+  <dimension ref="A1:L280"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -5148,150 +5156,161 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B266" s="1" t="s">
+    <row r="265" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H265" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I265" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="J265" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B267" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G266" s="1" t="s">
+      <c r="G267" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="H266" s="1" t="s">
+      <c r="H267" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I266" s="1" t="s">
+      <c r="I267" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J266" s="1">
+      <c r="J267" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H267" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="I267" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="J267" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="268" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H268" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="J268" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H269" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="I268" s="1" t="s">
+      <c r="I269" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="J268" s="1">
+      <c r="J269" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B270" s="1" t="s">
+    <row r="271" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B271" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G270" s="1" t="s">
+      <c r="G271" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H270" s="1" t="s">
+      <c r="H271" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I270" s="1" t="s">
+      <c r="I271" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J270" s="1">
+      <c r="J271" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H271" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="I271" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="J271" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="272" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H272" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I272" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J272" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H273" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I272" s="1" t="s">
+      <c r="I273" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="J272" s="1">
+      <c r="J273" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B274" s="1" t="s">
+    <row r="275" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B275" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="H274" s="1" t="s">
+      <c r="H275" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I274" s="1" t="s">
+      <c r="I275" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J274" s="1">
+      <c r="J275" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H275" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="I275" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="J275" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="276" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H276" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J276" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H277" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J277" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H278" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J278" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H279" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="I279" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J279" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H280" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="I279" s="1" t="s">
+      <c r="I280" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="J279" s="1">
+      <c r="J280" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6F50E1-996C-430F-AC8D-25CC76571CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E441EFD4-66B2-4A0A-9033-872344069A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="499">
   <si>
     <t>##var</t>
   </si>
@@ -1932,6 +1932,14 @@
   </si>
   <si>
     <t>返还</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VariantEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变式效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2302,7 +2310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L280"/>
+  <dimension ref="A1:L281"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -4998,319 +5006,330 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B250" s="1" t="s">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H249" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J249" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B251" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="H250" s="1" t="s">
+      <c r="H251" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I250" s="1" t="s">
+      <c r="I251" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J250" s="1">
+      <c r="J251" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H251" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="I251" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="J251" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="252" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H252" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J252" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H253" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="J253" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H254" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I253" s="1" t="s">
+      <c r="I254" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="J253" s="1">
+      <c r="J254" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B255" s="1" t="s">
+    <row r="256" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B256" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="G255" s="1" t="s">
+      <c r="G256" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="H255" s="1" t="s">
+      <c r="H256" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I255" s="1" t="s">
+      <c r="I256" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J255" s="1">
+      <c r="J256" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H256" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="I256" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="J256" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="257" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H257" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="J257" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H258" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J258" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H259" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I259" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J259" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H260" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="I259" s="1" t="s">
+      <c r="I260" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J259" s="1">
+      <c r="J260" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B261" s="1" t="s">
+    <row r="262" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B262" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="G261" s="1" t="s">
+      <c r="G262" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="H261" s="1" t="s">
+      <c r="H262" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I261" s="1" t="s">
+      <c r="I262" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J261" s="1">
+      <c r="J262" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H262" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="I262" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="J262" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="263" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H263" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J263" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H264" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J264" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H265" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I265" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="J265" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H266" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="I265" s="1" t="s">
+      <c r="I266" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="J265" s="1">
+      <c r="J266" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B267" s="1" t="s">
+    <row r="268" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B268" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G267" s="1" t="s">
+      <c r="G268" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="H267" s="1" t="s">
+      <c r="H268" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I267" s="1" t="s">
+      <c r="I268" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J267" s="1">
+      <c r="J268" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H268" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="I268" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="J268" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="269" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H269" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I269" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="J269" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H270" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="I269" s="1" t="s">
+      <c r="I270" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="J269" s="1">
+      <c r="J270" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B271" s="1" t="s">
+    <row r="272" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B272" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G271" s="1" t="s">
+      <c r="G272" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H271" s="1" t="s">
+      <c r="H272" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I271" s="1" t="s">
+      <c r="I272" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J271" s="1">
+      <c r="J272" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H272" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="I272" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="J272" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="273" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H273" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I273" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J273" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H274" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I273" s="1" t="s">
+      <c r="I274" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="J273" s="1">
+      <c r="J274" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B275" s="1" t="s">
+    <row r="276" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B276" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="H275" s="1" t="s">
+      <c r="H276" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I275" s="1" t="s">
+      <c r="I276" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J275" s="1">
+      <c r="J276" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="276" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H276" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="I276" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="J276" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="277" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H277" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J277" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H278" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J278" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H279" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J279" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H280" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="I280" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J280" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H281" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="I280" s="1" t="s">
+      <c r="I281" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="J280" s="1">
+      <c r="J281" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Luban/Config/Datas/__enums__.xlsx
+++ b/Luban/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E441EFD4-66B2-4A0A-9033-872344069A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC15957A-ABCA-46E6-BBF8-10E083CAB15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5565" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1300,14 +1300,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WeatherType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天气类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>晴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1940,6 +1932,14 @@
   </si>
   <si>
     <t>变式效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleWeatherType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗天气类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="40" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H40" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J40" s="1">
         <v>20066</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="46" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H46" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J46" s="1">
         <v>20076</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J52" s="1">
         <v>20086</v>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H58" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J58" s="1">
         <v>20096</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H64" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J64" s="1">
         <v>20106</v>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.2">
       <c r="H70" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J70" s="1">
         <v>20116</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H87" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>323</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H88" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>324</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J116" s="1">
         <v>16</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H120" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J120" s="1">
         <v>20</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H121" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J121" s="1">
         <v>21</v>
@@ -3694,7 +3694,7 @@
         <v>269</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J122" s="1">
         <v>22</v>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>186</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H127" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J127" s="1">
         <v>3</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H128" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J128" s="1">
         <v>4</v>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H129" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J129" s="1">
         <v>5</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H130" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J130" s="1">
         <v>6</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H134" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>277</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H135" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J135" s="1">
         <v>11</v>
@@ -3854,7 +3854,7 @@
         <v>180</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J137" s="1">
         <v>13</v>
@@ -3934,10 +3934,10 @@
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H145" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I145" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="J145" s="1">
         <v>6</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H198" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J198" s="1">
         <v>4</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H199" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J199" s="1">
         <v>5</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="200" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H200" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J200" s="1">
         <v>6</v>
@@ -4599,10 +4599,10 @@
     </row>
     <row r="211" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B211" s="1" t="s">
-        <v>338</v>
+        <v>497</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>339</v>
+        <v>498</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>186</v>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H212" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J212" s="1">
         <v>1</v>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H213" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J213" s="1">
         <v>2</v>
@@ -4638,10 +4638,10 @@
     </row>
     <row r="214" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H214" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J214" s="1">
         <v>3</v>
@@ -4649,10 +4649,10 @@
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H215" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J215" s="1">
         <v>4</v>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B217" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>186</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H218" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J218" s="1">
         <v>1</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H219" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J219" s="1">
         <v>2</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H220" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J220" s="1">
         <v>3</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H221" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J221" s="1">
         <v>4</v>
@@ -4721,10 +4721,10 @@
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B223" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>186</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H224" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J224" s="1">
         <v>2</v>
@@ -4749,10 +4749,10 @@
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H225" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J225" s="1">
         <v>3</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H226" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J226" s="1">
         <v>4</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H227" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J227" s="1">
         <v>5</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H228" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J228" s="1">
         <v>6</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H229" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J229" s="1">
         <v>7</v>
@@ -4804,10 +4804,10 @@
     </row>
     <row r="230" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H230" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J230" s="1">
         <v>8</v>
@@ -4815,10 +4815,10 @@
     </row>
     <row r="231" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H231" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J231" s="1">
         <v>9</v>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H232" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J232" s="1">
         <v>10</v>
@@ -4837,10 +4837,10 @@
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H233" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J233" s="1">
         <v>11</v>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H234" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J234" s="1">
         <v>12</v>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="235" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H235" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J235" s="1">
         <v>13</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="236" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H236" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J236" s="1">
         <v>14</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H237" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J237" s="1">
         <v>15</v>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="238" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H238" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J238" s="1">
         <v>16</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B240" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>186</v>
@@ -4920,10 +4920,10 @@
     </row>
     <row r="241" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H241" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J241" s="1">
         <v>1</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="242" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H242" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J242" s="1">
         <v>2</v>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="243" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H243" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J243" s="1">
         <v>3</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="244" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H244" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J244" s="1">
         <v>4</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="245" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H245" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J245" s="1">
         <v>5</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="246" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H246" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J246" s="1">
         <v>6</v>
@@ -4986,10 +4986,10 @@
     </row>
     <row r="247" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H247" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J247" s="1">
         <v>7</v>
@@ -4997,10 +4997,10 @@
     </row>
     <row r="248" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H248" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J248" s="1">
         <v>8</v>
@@ -5008,10 +5008,10 @@
     </row>
     <row r="249" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H249" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J249" s="1">
         <v>9</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="251" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B251" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>186</v>
@@ -5033,10 +5033,10 @@
     </row>
     <row r="252" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H252" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J252" s="1">
         <v>1</v>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="253" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H253" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J253" s="1">
         <v>2</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="254" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H254" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J254" s="1">
         <v>3</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="256" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B256" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H256" s="1" t="s">
         <v>186</v>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="257" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H257" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J257" s="1">
         <v>1</v>
@@ -5094,10 +5094,10 @@
     </row>
     <row r="258" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H258" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J258" s="1">
         <v>2</v>
@@ -5105,10 +5105,10 @@
     </row>
     <row r="259" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H259" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J259" s="1">
         <v>3</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="260" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H260" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J260" s="1">
         <v>4</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="262" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B262" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H262" s="1" t="s">
         <v>186</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="263" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H263" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="I263" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="I263" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="J263" s="1">
         <v>1</v>
@@ -5155,10 +5155,10 @@
     </row>
     <row r="264" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H264" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="I264" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="I264" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="J264" s="1">
         <v>2</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="265" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H265" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J265" s="1">
         <v>3</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="266" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H266" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J266" s="1">
         <v>4</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="268" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B268" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H268" s="1" t="s">
         <v>186</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="269" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H269" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J269" s="1">
         <v>1</v>
@@ -5216,10 +5216,10 @@
     </row>
     <row r="270" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H270" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J270" s="1">
         <v>2</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="272" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B272" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H272" s="1" t="s">
         <v>186</v>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="273" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H273" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I273" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="I273" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="J273" s="1">
         <v>1</v>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="274" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H274" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I274" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="I274" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="J274" s="1">
         <v>2</v>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="276" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B276" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>186</v>
@@ -5280,10 +5280,10 @@
     </row>
     <row r="277" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H277" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J277" s="1">
         <v>1</v>
@@ -5291,10 +5291,10 @@
     </row>
     <row r="278" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H278" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J278" s="1">
         <v>2</v>
@@ -5302,10 +5302,10 @@
     </row>
     <row r="279" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H279" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J279" s="1">
         <v>3</v>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="280" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H280" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J280" s="1">
         <v>4</v>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="281" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H281" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J281" s="1">
         <v>5</v>
